--- a/TC_Measurement_Data.xlsx
+++ b/TC_Measurement_Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jacobcn2\Documents\Thermal Conductivity Model\Code\TC_Comparison_Code\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://liveutk-my.sharepoint.com/personal/jnumbers_vols_utk_edu/Documents/Documents/2026-Structural-Coherence-Model/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C4E62733-C08C-4ABA-84A1-FEF52F230632}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="30" documentId="13_ncr:1_{C4E62733-C08C-4ABA-84A1-FEF52F230632}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{547EE345-4960-4B4C-B65D-953D678455F7}"/>
   <bookViews>
-    <workbookView xWindow="14220" yWindow="1080" windowWidth="14055" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,11 +23,24 @@
     <definedName name="ExternalData_1" localSheetId="3">'Robertson1.3CoF2'!$A$1:$C$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1266" uniqueCount="177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1270" uniqueCount="177">
   <si>
     <t>Thermal Diffusivity (m^2/s)</t>
   </si>
@@ -204,9 +217,6 @@
   </si>
   <si>
     <t>0.345NaF-0.59KF-0.065MgF2 (BYU)</t>
-  </si>
-  <si>
-    <t>0.6LiF-0.4NaF (BYU)</t>
   </si>
   <si>
     <t>0.465LiF-0.115NaF-0.42KF (Gallagher, 2022)</t>
@@ -497,9 +507,6 @@
     <t>0.52NaCl-0.48CaCl2 (Tian, 2021)</t>
   </si>
   <si>
-    <t>CaCl2 (Janze, 1978)</t>
-  </si>
-  <si>
     <t>CaCl2 (Wei, 2022; MD)</t>
   </si>
   <si>
@@ -558,6 +565,12 @@
   </si>
   <si>
     <t>0.535NaCl-0.315MgCl2-0.15CaCl2 (Wei, 2022; MD)</t>
+  </si>
+  <si>
+    <t>CaCl2 (Janz, 1978)</t>
+  </si>
+  <si>
+    <t>0.6LiF-0.4NaF (Ruth, 2023)</t>
   </si>
 </sst>
 </file>
@@ -839,6 +852,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1142,7 +1159,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:N847"/>
+  <dimension ref="A1:N851"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="7.85546875" style="2" customWidth="1"/>
@@ -1186,7 +1203,7 @@
         <v>43</v>
       </c>
       <c r="J1" s="30" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="M1" s="30"/>
       <c r="N1" s="30"/>
@@ -1196,7 +1213,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="33" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C2" s="30" t="s">
         <v>44</v>
@@ -1224,7 +1241,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C3" s="30" t="s">
         <v>44</v>
@@ -1244,7 +1261,7 @@
         <v>1</v>
       </c>
       <c r="B4" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C4" s="30" t="s">
         <v>44</v>
@@ -1264,7 +1281,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C5" s="30" t="s">
         <v>44</v>
@@ -1284,7 +1301,7 @@
         <v>1</v>
       </c>
       <c r="B6" s="35" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C6" s="30" t="s">
         <v>44</v>
@@ -1304,7 +1321,7 @@
         <v>2</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C7" s="30" t="s">
         <v>46</v>
@@ -1332,7 +1349,7 @@
         <v>2</v>
       </c>
       <c r="B8" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C8" s="30" t="s">
         <v>46</v>
@@ -1352,7 +1369,7 @@
         <v>2</v>
       </c>
       <c r="B9" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C9" s="30" t="s">
         <v>46</v>
@@ -1372,7 +1389,7 @@
         <v>2</v>
       </c>
       <c r="B10" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C10" s="30" t="s">
         <v>46</v>
@@ -1392,7 +1409,7 @@
         <v>2</v>
       </c>
       <c r="B11" s="35" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="C11" s="30" t="s">
         <v>46</v>
@@ -1412,7 +1429,7 @@
         <v>3</v>
       </c>
       <c r="B12" s="33" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C12" s="30" t="s">
         <v>47</v>
@@ -1440,7 +1457,7 @@
         <v>3</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C13" s="30" t="s">
         <v>47</v>
@@ -1460,7 +1477,7 @@
         <v>3</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C14" s="30" t="s">
         <v>47</v>
@@ -1480,7 +1497,7 @@
         <v>3</v>
       </c>
       <c r="B15" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C15" s="30" t="s">
         <v>47</v>
@@ -1500,7 +1517,7 @@
         <v>3</v>
       </c>
       <c r="B16" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C16" s="30" t="s">
         <v>47</v>
@@ -1520,7 +1537,7 @@
         <v>3</v>
       </c>
       <c r="B17" s="30" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="C17" s="30" t="s">
         <v>47</v>
@@ -2628,7 +2645,7 @@
         <v>13</v>
       </c>
       <c r="B69" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D69" s="34">
         <v>761.2</v>
@@ -2654,7 +2671,7 @@
         <v>13</v>
       </c>
       <c r="B70" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D70" s="34">
         <v>811.3</v>
@@ -2680,7 +2697,7 @@
         <v>13</v>
       </c>
       <c r="B71" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D71" s="34">
         <v>860.5</v>
@@ -2706,7 +2723,7 @@
         <v>13</v>
       </c>
       <c r="B72" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D72" s="34">
         <v>908.5</v>
@@ -2732,7 +2749,7 @@
         <v>13</v>
       </c>
       <c r="B73" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D73" s="34">
         <v>958.5</v>
@@ -2758,7 +2775,7 @@
         <v>13</v>
       </c>
       <c r="B74" s="30" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D74" s="34">
         <v>1008.2</v>
@@ -2784,7 +2801,7 @@
         <v>14</v>
       </c>
       <c r="B75" s="30" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="D75" s="34">
         <v>933.1</v>
@@ -2818,7 +2835,7 @@
         <v>14</v>
       </c>
       <c r="B76" s="30" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="D76" s="34">
         <v>950.7</v>
@@ -2844,7 +2861,7 @@
         <v>14</v>
       </c>
       <c r="B77" s="30" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="D77" s="34">
         <v>966.7</v>
@@ -2870,7 +2887,7 @@
         <v>14</v>
       </c>
       <c r="B78" s="30" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="D78" s="34">
         <v>986.7</v>
@@ -2896,7 +2913,7 @@
         <v>14</v>
       </c>
       <c r="B79" s="30" t="s">
-        <v>59</v>
+        <v>176</v>
       </c>
       <c r="D79" s="34">
         <v>1006.9</v>
@@ -2922,7 +2939,7 @@
         <v>15</v>
       </c>
       <c r="B80" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D80" s="34">
         <v>834.2</v>
@@ -2940,7 +2957,7 @@
         <v>45</v>
       </c>
       <c r="I80" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J80" s="30" t="s">
         <v>56</v>
@@ -2951,7 +2968,7 @@
         <v>15</v>
       </c>
       <c r="B81" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D81" s="34">
         <v>833.8</v>
@@ -2969,7 +2986,7 @@
         <v>45</v>
       </c>
       <c r="I81" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J81" s="30" t="s">
         <v>56</v>
@@ -2980,7 +2997,7 @@
         <v>15</v>
       </c>
       <c r="B82" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D82" s="34">
         <v>946.2</v>
@@ -2998,7 +3015,7 @@
         <v>45</v>
       </c>
       <c r="I82" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J82" s="30" t="s">
         <v>56</v>
@@ -3009,7 +3026,7 @@
         <v>15</v>
       </c>
       <c r="B83" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D83" s="34">
         <v>945.8</v>
@@ -3027,7 +3044,7 @@
         <v>45</v>
       </c>
       <c r="I83" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J83" s="30" t="s">
         <v>56</v>
@@ -3038,7 +3055,7 @@
         <v>15</v>
       </c>
       <c r="B84" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D84" s="34">
         <v>1024.9000000000001</v>
@@ -3056,7 +3073,7 @@
         <v>45</v>
       </c>
       <c r="I84" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J84" s="30" t="s">
         <v>56</v>
@@ -3067,7 +3084,7 @@
         <v>15</v>
       </c>
       <c r="B85" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D85" s="34">
         <v>1024.5</v>
@@ -3085,7 +3102,7 @@
         <v>45</v>
       </c>
       <c r="I85" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J85" s="30" t="s">
         <v>56</v>
@@ -3096,7 +3113,7 @@
         <v>15</v>
       </c>
       <c r="B86" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D86" s="34">
         <v>1024.5</v>
@@ -3114,7 +3131,7 @@
         <v>45</v>
       </c>
       <c r="I86" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J86" s="30" t="s">
         <v>56</v>
@@ -3125,7 +3142,7 @@
         <v>15</v>
       </c>
       <c r="B87" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D87" s="32">
         <v>1100</v>
@@ -3143,7 +3160,7 @@
         <v>45</v>
       </c>
       <c r="I87" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J87" s="30" t="s">
         <v>56</v>
@@ -3154,7 +3171,7 @@
         <v>15</v>
       </c>
       <c r="B88" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D88" s="32">
         <v>1100</v>
@@ -3172,7 +3189,7 @@
         <v>45</v>
       </c>
       <c r="I88" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J88" s="30" t="s">
         <v>56</v>
@@ -3183,7 +3200,7 @@
         <v>15</v>
       </c>
       <c r="B89" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D89" s="32">
         <v>1100</v>
@@ -3201,7 +3218,7 @@
         <v>45</v>
       </c>
       <c r="I89" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J89" s="30" t="s">
         <v>56</v>
@@ -3212,7 +3229,7 @@
         <v>15</v>
       </c>
       <c r="B90" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D90" s="32">
         <v>1195</v>
@@ -3230,7 +3247,7 @@
         <v>45</v>
       </c>
       <c r="I90" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J90" s="30" t="s">
         <v>56</v>
@@ -3241,7 +3258,7 @@
         <v>15</v>
       </c>
       <c r="B91" s="30" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D91" s="32">
         <v>1195</v>
@@ -3259,7 +3276,7 @@
         <v>45</v>
       </c>
       <c r="I91" s="30" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="J91" s="30" t="s">
         <v>56</v>
@@ -3270,7 +3287,7 @@
         <v>16</v>
       </c>
       <c r="B92" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D92" s="34">
         <v>812.64</v>
@@ -3282,7 +3299,7 @@
         <v>0.34699999999999998</v>
       </c>
       <c r="I92" s="30" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="J92" s="30" t="s">
         <v>56</v>
@@ -3293,7 +3310,7 @@
         <v>16</v>
       </c>
       <c r="B93" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D93" s="34">
         <v>892.73</v>
@@ -3313,7 +3330,7 @@
         <v>16</v>
       </c>
       <c r="B94" s="30" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D94" s="34">
         <v>962.53</v>
@@ -3333,7 +3350,7 @@
         <v>17</v>
       </c>
       <c r="B95" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D95" s="34">
         <v>771.03</v>
@@ -3342,7 +3359,7 @@
         <v>2.39</v>
       </c>
       <c r="I95" s="30" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="J95" s="30" t="s">
         <v>56</v>
@@ -3353,7 +3370,7 @@
         <v>17</v>
       </c>
       <c r="B96" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D96" s="34">
         <v>801.01</v>
@@ -3370,7 +3387,7 @@
         <v>17</v>
       </c>
       <c r="B97" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D97" s="34">
         <v>852.01</v>
@@ -3387,7 +3404,7 @@
         <v>17</v>
       </c>
       <c r="B98" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D98" s="34">
         <v>922.71</v>
@@ -3404,7 +3421,7 @@
         <v>17</v>
       </c>
       <c r="B99" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D99" s="34">
         <v>1039.9000000000001</v>
@@ -3421,7 +3438,7 @@
         <v>17</v>
       </c>
       <c r="B100" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D100" s="34">
         <v>1119.5999999999999</v>
@@ -3438,7 +3455,7 @@
         <v>17</v>
       </c>
       <c r="B101" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D101" s="34">
         <v>855.649</v>
@@ -3455,7 +3472,7 @@
         <v>17</v>
       </c>
       <c r="B102" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D102" s="34">
         <v>871.25</v>
@@ -3472,7 +3489,7 @@
         <v>17</v>
       </c>
       <c r="B103" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D103" s="34">
         <v>902.13</v>
@@ -3489,7 +3506,7 @@
         <v>17</v>
       </c>
       <c r="B104" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D104" s="34">
         <v>932.1</v>
@@ -3506,7 +3523,7 @@
         <v>17</v>
       </c>
       <c r="B105" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D105" s="34">
         <v>974.16</v>
@@ -3523,7 +3540,7 @@
         <v>17</v>
       </c>
       <c r="B106" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D106" s="34">
         <v>1012.2</v>
@@ -3540,7 +3557,7 @@
         <v>17</v>
       </c>
       <c r="B107" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D107" s="34">
         <v>1050.2</v>
@@ -3557,7 +3574,7 @@
         <v>17</v>
       </c>
       <c r="B108" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D108" s="34">
         <v>799.66</v>
@@ -3574,7 +3591,7 @@
         <v>17</v>
       </c>
       <c r="B109" s="30" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D109" s="34">
         <v>925.39</v>
@@ -3591,7 +3608,7 @@
         <v>18</v>
       </c>
       <c r="B110" s="30" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D110" s="34">
         <v>772.82</v>
@@ -3603,7 +3620,7 @@
         <v>8.9999999999999993E-3</v>
       </c>
       <c r="I110" s="30" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="J110" s="30" t="s">
         <v>56</v>
@@ -3614,7 +3631,7 @@
         <v>19</v>
       </c>
       <c r="B111" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D111" s="34">
         <v>793.36</v>
@@ -3626,7 +3643,7 @@
         <v>3.2000000000000001E-2</v>
       </c>
       <c r="I111" s="30" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="J111" s="30" t="s">
         <v>56</v>
@@ -3637,7 +3654,7 @@
         <v>19</v>
       </c>
       <c r="B112" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D112" s="34">
         <v>818.46</v>
@@ -3657,7 +3674,7 @@
         <v>19</v>
       </c>
       <c r="B113" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D113" s="34">
         <v>851.01</v>
@@ -3677,7 +3694,7 @@
         <v>19</v>
       </c>
       <c r="B114" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D114" s="34">
         <v>877.52</v>
@@ -3697,7 +3714,7 @@
         <v>19</v>
       </c>
       <c r="B115" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D115" s="34">
         <v>907.38</v>
@@ -3717,7 +3734,7 @@
         <v>19</v>
       </c>
       <c r="B116" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D116" s="34">
         <v>924.05</v>
@@ -3737,7 +3754,7 @@
         <v>19</v>
       </c>
       <c r="B117" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D117" s="34">
         <v>942.05</v>
@@ -3757,7 +3774,7 @@
         <v>19</v>
       </c>
       <c r="B118" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D118" s="34">
         <v>942.39</v>
@@ -3777,7 +3794,7 @@
         <v>19</v>
       </c>
       <c r="B119" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D119" s="34">
         <v>1016.7</v>
@@ -3797,7 +3814,7 @@
         <v>19</v>
       </c>
       <c r="B120" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D120" s="32">
         <v>1047</v>
@@ -3817,7 +3834,7 @@
         <v>19</v>
       </c>
       <c r="B121" s="30" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D121" s="34">
         <v>1073.5</v>
@@ -3837,7 +3854,7 @@
         <v>20</v>
       </c>
       <c r="B122" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D122" s="34">
         <v>780.55</v>
@@ -3849,7 +3866,7 @@
         <v>3.3000000000000002E-2</v>
       </c>
       <c r="I122" s="30" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="J122" s="30" t="s">
         <v>56</v>
@@ -3860,7 +3877,7 @@
         <v>20</v>
       </c>
       <c r="B123" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D123" s="34">
         <v>816.85</v>
@@ -3880,7 +3897,7 @@
         <v>20</v>
       </c>
       <c r="B124" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D124" s="34">
         <v>882.18</v>
@@ -3900,7 +3917,7 @@
         <v>20</v>
       </c>
       <c r="B125" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D125" s="34">
         <v>950.5</v>
@@ -3920,7 +3937,7 @@
         <v>20</v>
       </c>
       <c r="B126" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D126" s="34">
         <v>1029.9000000000001</v>
@@ -3940,7 +3957,7 @@
         <v>20</v>
       </c>
       <c r="B127" s="30" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D127" s="32">
         <v>1079</v>
@@ -3960,7 +3977,7 @@
         <v>21</v>
       </c>
       <c r="B128" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D128" s="34">
         <v>742.4</v>
@@ -3972,7 +3989,7 @@
         <v>6.3E-2</v>
       </c>
       <c r="I128" s="30" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J128" s="30" t="s">
         <v>56</v>
@@ -3983,7 +4000,7 @@
         <v>21</v>
       </c>
       <c r="B129" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D129" s="32">
         <v>747</v>
@@ -4003,7 +4020,7 @@
         <v>21</v>
       </c>
       <c r="B130" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D130" s="34">
         <v>747.8</v>
@@ -4023,7 +4040,7 @@
         <v>21</v>
       </c>
       <c r="B131" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D131" s="34">
         <v>747.8</v>
@@ -4043,7 +4060,7 @@
         <v>21</v>
       </c>
       <c r="B132" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D132" s="34">
         <v>747.8</v>
@@ -4063,7 +4080,7 @@
         <v>21</v>
       </c>
       <c r="B133" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D133" s="34">
         <v>762.6</v>
@@ -4083,7 +4100,7 @@
         <v>21</v>
       </c>
       <c r="B134" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D134" s="34">
         <v>762.8</v>
@@ -4103,7 +4120,7 @@
         <v>21</v>
       </c>
       <c r="B135" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D135" s="34">
         <v>772.2</v>
@@ -4123,7 +4140,7 @@
         <v>21</v>
       </c>
       <c r="B136" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D136" s="34">
         <v>772.5</v>
@@ -4143,7 +4160,7 @@
         <v>21</v>
       </c>
       <c r="B137" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D137" s="34">
         <v>772.4</v>
@@ -4163,7 +4180,7 @@
         <v>21</v>
       </c>
       <c r="B138" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D138" s="32">
         <v>783</v>
@@ -4183,7 +4200,7 @@
         <v>21</v>
       </c>
       <c r="B139" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D139" s="34">
         <v>783.4</v>
@@ -4203,7 +4220,7 @@
         <v>21</v>
       </c>
       <c r="B140" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D140" s="34">
         <v>797.7</v>
@@ -4223,7 +4240,7 @@
         <v>21</v>
       </c>
       <c r="B141" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D141" s="34">
         <v>797.6</v>
@@ -4243,7 +4260,7 @@
         <v>21</v>
       </c>
       <c r="B142" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D142" s="34">
         <v>802.1</v>
@@ -4263,7 +4280,7 @@
         <v>21</v>
       </c>
       <c r="B143" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D143" s="34">
         <v>822.4</v>
@@ -4283,7 +4300,7 @@
         <v>21</v>
       </c>
       <c r="B144" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D144" s="34">
         <v>847.7</v>
@@ -4303,7 +4320,7 @@
         <v>21</v>
       </c>
       <c r="B145" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D145" s="34">
         <v>798.1</v>
@@ -4323,7 +4340,7 @@
         <v>21</v>
       </c>
       <c r="B146" s="30" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D146" s="34">
         <v>797.8</v>
@@ -4343,7 +4360,7 @@
         <v>22</v>
       </c>
       <c r="B147" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D147" s="34">
         <v>773.29</v>
@@ -4355,7 +4372,7 @@
         <v>1.6E-2</v>
       </c>
       <c r="I147" s="30" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J147" s="30" t="s">
         <v>56</v>
@@ -4366,7 +4383,7 @@
         <v>22</v>
       </c>
       <c r="B148" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D148" s="34">
         <v>823.68</v>
@@ -4386,7 +4403,7 @@
         <v>22</v>
       </c>
       <c r="B149" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D149" s="34">
         <v>873.04</v>
@@ -4406,7 +4423,7 @@
         <v>22</v>
       </c>
       <c r="B150" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D150" s="34">
         <v>922.75</v>
@@ -4426,7 +4443,7 @@
         <v>22</v>
       </c>
       <c r="B151" s="30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="D151" s="34">
         <v>972.71</v>
@@ -4446,7 +4463,7 @@
         <v>32</v>
       </c>
       <c r="B152" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D152" s="32">
         <v>750</v>
@@ -4460,7 +4477,7 @@
         <v>32</v>
       </c>
       <c r="B153" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D153" s="32">
         <v>751</v>
@@ -4474,7 +4491,7 @@
         <v>32</v>
       </c>
       <c r="B154" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D154" s="32">
         <v>752</v>
@@ -4488,7 +4505,7 @@
         <v>32</v>
       </c>
       <c r="B155" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D155" s="32">
         <v>753</v>
@@ -4502,7 +4519,7 @@
         <v>32</v>
       </c>
       <c r="B156" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D156" s="32">
         <v>754</v>
@@ -4516,7 +4533,7 @@
         <v>32</v>
       </c>
       <c r="B157" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D157" s="32">
         <v>755</v>
@@ -4530,7 +4547,7 @@
         <v>32</v>
       </c>
       <c r="B158" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D158" s="32">
         <v>756</v>
@@ -4544,7 +4561,7 @@
         <v>32</v>
       </c>
       <c r="B159" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D159" s="32">
         <v>757</v>
@@ -4558,7 +4575,7 @@
         <v>32</v>
       </c>
       <c r="B160" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D160" s="32">
         <v>758</v>
@@ -4572,7 +4589,7 @@
         <v>32</v>
       </c>
       <c r="B161" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D161" s="32">
         <v>759</v>
@@ -4586,7 +4603,7 @@
         <v>32</v>
       </c>
       <c r="B162" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D162" s="32">
         <v>760</v>
@@ -4600,7 +4617,7 @@
         <v>32</v>
       </c>
       <c r="B163" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D163" s="32">
         <v>761</v>
@@ -4614,7 +4631,7 @@
         <v>32</v>
       </c>
       <c r="B164" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D164" s="32">
         <v>762</v>
@@ -4628,7 +4645,7 @@
         <v>32</v>
       </c>
       <c r="B165" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D165" s="32">
         <v>763</v>
@@ -4642,7 +4659,7 @@
         <v>32</v>
       </c>
       <c r="B166" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D166" s="32">
         <v>764</v>
@@ -4656,7 +4673,7 @@
         <v>32</v>
       </c>
       <c r="B167" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D167" s="32">
         <v>765</v>
@@ -4670,7 +4687,7 @@
         <v>32</v>
       </c>
       <c r="B168" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D168" s="32">
         <v>766</v>
@@ -4684,7 +4701,7 @@
         <v>32</v>
       </c>
       <c r="B169" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D169" s="32">
         <v>767</v>
@@ -4698,7 +4715,7 @@
         <v>32</v>
       </c>
       <c r="B170" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D170" s="32">
         <v>768</v>
@@ -4712,7 +4729,7 @@
         <v>32</v>
       </c>
       <c r="B171" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D171" s="32">
         <v>769</v>
@@ -4726,7 +4743,7 @@
         <v>32</v>
       </c>
       <c r="B172" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D172" s="32">
         <v>770</v>
@@ -4740,7 +4757,7 @@
         <v>32</v>
       </c>
       <c r="B173" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D173" s="32">
         <v>771</v>
@@ -4754,7 +4771,7 @@
         <v>32</v>
       </c>
       <c r="B174" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D174" s="32">
         <v>772</v>
@@ -4768,7 +4785,7 @@
         <v>32</v>
       </c>
       <c r="B175" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D175" s="32">
         <v>773</v>
@@ -4782,7 +4799,7 @@
         <v>32</v>
       </c>
       <c r="B176" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D176" s="32">
         <v>774</v>
@@ -4796,7 +4813,7 @@
         <v>32</v>
       </c>
       <c r="B177" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D177" s="32">
         <v>775</v>
@@ -4810,7 +4827,7 @@
         <v>32</v>
       </c>
       <c r="B178" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D178" s="32">
         <v>776</v>
@@ -4824,7 +4841,7 @@
         <v>32</v>
       </c>
       <c r="B179" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D179" s="32">
         <v>777</v>
@@ -4838,7 +4855,7 @@
         <v>32</v>
       </c>
       <c r="B180" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D180" s="32">
         <v>778</v>
@@ -4852,7 +4869,7 @@
         <v>32</v>
       </c>
       <c r="B181" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D181" s="32">
         <v>779</v>
@@ -4866,7 +4883,7 @@
         <v>32</v>
       </c>
       <c r="B182" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D182" s="32">
         <v>780</v>
@@ -4880,7 +4897,7 @@
         <v>32</v>
       </c>
       <c r="B183" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D183" s="32">
         <v>781</v>
@@ -4894,7 +4911,7 @@
         <v>32</v>
       </c>
       <c r="B184" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D184" s="32">
         <v>782</v>
@@ -4908,7 +4925,7 @@
         <v>32</v>
       </c>
       <c r="B185" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D185" s="32">
         <v>783</v>
@@ -4922,7 +4939,7 @@
         <v>32</v>
       </c>
       <c r="B186" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D186" s="32">
         <v>784</v>
@@ -4936,7 +4953,7 @@
         <v>32</v>
       </c>
       <c r="B187" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D187" s="32">
         <v>785</v>
@@ -4950,7 +4967,7 @@
         <v>32</v>
       </c>
       <c r="B188" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D188" s="32">
         <v>786</v>
@@ -4964,7 +4981,7 @@
         <v>32</v>
       </c>
       <c r="B189" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D189" s="32">
         <v>787</v>
@@ -4978,7 +4995,7 @@
         <v>32</v>
       </c>
       <c r="B190" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D190" s="32">
         <v>788</v>
@@ -4992,7 +5009,7 @@
         <v>32</v>
       </c>
       <c r="B191" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D191" s="32">
         <v>789</v>
@@ -5006,7 +5023,7 @@
         <v>32</v>
       </c>
       <c r="B192" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D192" s="32">
         <v>790</v>
@@ -5020,7 +5037,7 @@
         <v>32</v>
       </c>
       <c r="B193" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D193" s="32">
         <v>791</v>
@@ -5034,7 +5051,7 @@
         <v>32</v>
       </c>
       <c r="B194" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D194" s="32">
         <v>792</v>
@@ -5048,7 +5065,7 @@
         <v>32</v>
       </c>
       <c r="B195" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D195" s="32">
         <v>793</v>
@@ -5062,7 +5079,7 @@
         <v>32</v>
       </c>
       <c r="B196" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D196" s="32">
         <v>794</v>
@@ -5076,7 +5093,7 @@
         <v>32</v>
       </c>
       <c r="B197" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D197" s="32">
         <v>795</v>
@@ -5090,7 +5107,7 @@
         <v>32</v>
       </c>
       <c r="B198" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D198" s="32">
         <v>796</v>
@@ -5104,7 +5121,7 @@
         <v>32</v>
       </c>
       <c r="B199" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D199" s="32">
         <v>797</v>
@@ -5118,7 +5135,7 @@
         <v>32</v>
       </c>
       <c r="B200" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D200" s="32">
         <v>798</v>
@@ -5132,7 +5149,7 @@
         <v>32</v>
       </c>
       <c r="B201" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D201" s="32">
         <v>799</v>
@@ -5146,7 +5163,7 @@
         <v>32</v>
       </c>
       <c r="B202" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D202" s="32">
         <v>800</v>
@@ -5160,7 +5177,7 @@
         <v>32</v>
       </c>
       <c r="B203" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D203" s="32">
         <v>801</v>
@@ -5174,7 +5191,7 @@
         <v>32</v>
       </c>
       <c r="B204" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D204" s="32">
         <v>802</v>
@@ -5188,7 +5205,7 @@
         <v>32</v>
       </c>
       <c r="B205" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D205" s="32">
         <v>803</v>
@@ -5202,7 +5219,7 @@
         <v>32</v>
       </c>
       <c r="B206" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D206" s="32">
         <v>804</v>
@@ -5216,7 +5233,7 @@
         <v>32</v>
       </c>
       <c r="B207" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D207" s="32">
         <v>805</v>
@@ -5230,7 +5247,7 @@
         <v>32</v>
       </c>
       <c r="B208" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D208" s="32">
         <v>806</v>
@@ -5244,7 +5261,7 @@
         <v>32</v>
       </c>
       <c r="B209" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D209" s="32">
         <v>807</v>
@@ -5258,7 +5275,7 @@
         <v>32</v>
       </c>
       <c r="B210" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D210" s="32">
         <v>808</v>
@@ -5272,7 +5289,7 @@
         <v>32</v>
       </c>
       <c r="B211" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D211" s="32">
         <v>809</v>
@@ -5286,7 +5303,7 @@
         <v>32</v>
       </c>
       <c r="B212" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D212" s="32">
         <v>810</v>
@@ -5300,7 +5317,7 @@
         <v>32</v>
       </c>
       <c r="B213" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D213" s="32">
         <v>811</v>
@@ -5314,7 +5331,7 @@
         <v>32</v>
       </c>
       <c r="B214" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D214" s="32">
         <v>812</v>
@@ -5328,7 +5345,7 @@
         <v>32</v>
       </c>
       <c r="B215" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D215" s="32">
         <v>813</v>
@@ -5342,7 +5359,7 @@
         <v>32</v>
       </c>
       <c r="B216" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D216" s="32">
         <v>814</v>
@@ -5356,7 +5373,7 @@
         <v>32</v>
       </c>
       <c r="B217" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D217" s="32">
         <v>815</v>
@@ -5370,7 +5387,7 @@
         <v>32</v>
       </c>
       <c r="B218" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D218" s="32">
         <v>816</v>
@@ -5384,7 +5401,7 @@
         <v>32</v>
       </c>
       <c r="B219" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D219" s="32">
         <v>817</v>
@@ -5398,7 +5415,7 @@
         <v>32</v>
       </c>
       <c r="B220" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D220" s="32">
         <v>818</v>
@@ -5412,7 +5429,7 @@
         <v>32</v>
       </c>
       <c r="B221" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D221" s="32">
         <v>819</v>
@@ -5426,7 +5443,7 @@
         <v>32</v>
       </c>
       <c r="B222" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D222" s="32">
         <v>820</v>
@@ -5440,7 +5457,7 @@
         <v>32</v>
       </c>
       <c r="B223" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D223" s="32">
         <v>821</v>
@@ -5454,7 +5471,7 @@
         <v>32</v>
       </c>
       <c r="B224" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D224" s="32">
         <v>750</v>
@@ -5468,7 +5485,7 @@
         <v>32</v>
       </c>
       <c r="B225" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D225" s="32">
         <v>752</v>
@@ -5482,7 +5499,7 @@
         <v>32</v>
       </c>
       <c r="B226" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D226" s="32">
         <v>754</v>
@@ -5496,7 +5513,7 @@
         <v>32</v>
       </c>
       <c r="B227" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D227" s="32">
         <v>756</v>
@@ -5510,7 +5527,7 @@
         <v>32</v>
       </c>
       <c r="B228" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D228" s="32">
         <v>758</v>
@@ -5524,7 +5541,7 @@
         <v>32</v>
       </c>
       <c r="B229" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D229" s="32">
         <v>760</v>
@@ -5538,7 +5555,7 @@
         <v>32</v>
       </c>
       <c r="B230" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D230" s="32">
         <v>762</v>
@@ -5552,7 +5569,7 @@
         <v>32</v>
       </c>
       <c r="B231" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D231" s="32">
         <v>765</v>
@@ -5566,7 +5583,7 @@
         <v>32</v>
       </c>
       <c r="B232" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D232" s="32">
         <v>767</v>
@@ -5580,7 +5597,7 @@
         <v>32</v>
       </c>
       <c r="B233" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D233" s="32">
         <v>769</v>
@@ -5594,7 +5611,7 @@
         <v>32</v>
       </c>
       <c r="B234" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D234" s="32">
         <v>771</v>
@@ -5608,7 +5625,7 @@
         <v>32</v>
       </c>
       <c r="B235" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D235" s="32">
         <v>773</v>
@@ -5622,7 +5639,7 @@
         <v>32</v>
       </c>
       <c r="B236" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D236" s="32">
         <v>775</v>
@@ -5636,7 +5653,7 @@
         <v>32</v>
       </c>
       <c r="B237" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D237" s="32">
         <v>777</v>
@@ -5650,7 +5667,7 @@
         <v>32</v>
       </c>
       <c r="B238" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D238" s="32">
         <v>779</v>
@@ -5664,7 +5681,7 @@
         <v>32</v>
       </c>
       <c r="B239" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D239" s="32">
         <v>781</v>
@@ -5678,7 +5695,7 @@
         <v>32</v>
       </c>
       <c r="B240" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D240" s="32">
         <v>783</v>
@@ -5692,7 +5709,7 @@
         <v>32</v>
       </c>
       <c r="B241" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D241" s="32">
         <v>785</v>
@@ -5706,7 +5723,7 @@
         <v>32</v>
       </c>
       <c r="B242" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D242" s="32">
         <v>787</v>
@@ -5720,7 +5737,7 @@
         <v>32</v>
       </c>
       <c r="B243" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D243" s="32">
         <v>789</v>
@@ -5734,7 +5751,7 @@
         <v>32</v>
       </c>
       <c r="B244" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D244" s="32">
         <v>791</v>
@@ -5748,7 +5765,7 @@
         <v>32</v>
       </c>
       <c r="B245" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D245" s="32">
         <v>793</v>
@@ -5762,7 +5779,7 @@
         <v>32</v>
       </c>
       <c r="B246" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D246" s="32">
         <v>795</v>
@@ -5776,7 +5793,7 @@
         <v>32</v>
       </c>
       <c r="B247" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D247" s="32">
         <v>797</v>
@@ -5790,7 +5807,7 @@
         <v>32</v>
       </c>
       <c r="B248" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D248" s="32">
         <v>799</v>
@@ -5804,7 +5821,7 @@
         <v>32</v>
       </c>
       <c r="B249" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D249" s="32">
         <v>801</v>
@@ -5818,7 +5835,7 @@
         <v>32</v>
       </c>
       <c r="B250" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D250" s="32">
         <v>803</v>
@@ -5832,7 +5849,7 @@
         <v>32</v>
       </c>
       <c r="B251" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D251" s="32">
         <v>805</v>
@@ -5846,7 +5863,7 @@
         <v>32</v>
       </c>
       <c r="B252" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D252" s="32">
         <v>807</v>
@@ -5860,7 +5877,7 @@
         <v>32</v>
       </c>
       <c r="B253" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D253" s="32">
         <v>809</v>
@@ -5874,7 +5891,7 @@
         <v>32</v>
       </c>
       <c r="B254" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D254" s="32">
         <v>811</v>
@@ -5888,7 +5905,7 @@
         <v>32</v>
       </c>
       <c r="B255" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D255" s="32">
         <v>813</v>
@@ -5902,7 +5919,7 @@
         <v>32</v>
       </c>
       <c r="B256" s="30" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D256" s="32">
         <v>816</v>
@@ -5916,7 +5933,7 @@
         <v>23</v>
       </c>
       <c r="B257" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D257" s="34">
         <v>748.7</v>
@@ -5928,7 +5945,7 @@
         <v>8.1000000000000003E-2</v>
       </c>
       <c r="I257" s="30" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="J257" s="30" t="s">
         <v>56</v>
@@ -5939,7 +5956,7 @@
         <v>23</v>
       </c>
       <c r="B258" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D258" s="34">
         <v>759.9</v>
@@ -5959,7 +5976,7 @@
         <v>23</v>
       </c>
       <c r="B259" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D259" s="34">
         <v>771.1</v>
@@ -5979,7 +5996,7 @@
         <v>23</v>
       </c>
       <c r="B260" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D260" s="34">
         <v>782.3</v>
@@ -5999,7 +6016,7 @@
         <v>23</v>
       </c>
       <c r="B261" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D261" s="34">
         <v>793.5</v>
@@ -6019,7 +6036,7 @@
         <v>23</v>
       </c>
       <c r="B262" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D262" s="34">
         <v>804.7</v>
@@ -6039,7 +6056,7 @@
         <v>23</v>
       </c>
       <c r="B263" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D263" s="34">
         <v>815.9</v>
@@ -6059,7 +6076,7 @@
         <v>23</v>
       </c>
       <c r="B264" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D264" s="34">
         <v>827.2</v>
@@ -6079,7 +6096,7 @@
         <v>23</v>
       </c>
       <c r="B265" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D265" s="34">
         <v>838.4</v>
@@ -6099,7 +6116,7 @@
         <v>23</v>
       </c>
       <c r="B266" s="30" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D266" s="34">
         <v>852.8</v>
@@ -6119,7 +6136,7 @@
         <v>24</v>
       </c>
       <c r="B267" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D267" s="34">
         <v>808.97</v>
@@ -6141,7 +6158,7 @@
         <v>24</v>
       </c>
       <c r="B268" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D268" s="32">
         <v>802</v>
@@ -6155,7 +6172,7 @@
         <v>24</v>
       </c>
       <c r="B269" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D269" s="32">
         <v>804</v>
@@ -6169,7 +6186,7 @@
         <v>24</v>
       </c>
       <c r="B270" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D270" s="32">
         <v>804</v>
@@ -6183,7 +6200,7 @@
         <v>24</v>
       </c>
       <c r="B271" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D271" s="32">
         <v>804</v>
@@ -6197,7 +6214,7 @@
         <v>24</v>
       </c>
       <c r="B272" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D272" s="34">
         <v>915.86</v>
@@ -6211,7 +6228,7 @@
         <v>24</v>
       </c>
       <c r="B273" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D273" s="32">
         <v>916</v>
@@ -6225,7 +6242,7 @@
         <v>24</v>
       </c>
       <c r="B274" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D274" s="34">
         <v>912.69</v>
@@ -6239,7 +6256,7 @@
         <v>24</v>
       </c>
       <c r="B275" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D275" s="34">
         <v>912.75</v>
@@ -6253,7 +6270,7 @@
         <v>24</v>
       </c>
       <c r="B276" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D276" s="34">
         <v>1020.87</v>
@@ -6267,7 +6284,7 @@
         <v>24</v>
       </c>
       <c r="B277" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D277" s="34">
         <v>1021.07</v>
@@ -6281,7 +6298,7 @@
         <v>24</v>
       </c>
       <c r="B278" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D278" s="34">
         <v>1021.03</v>
@@ -6295,7 +6312,7 @@
         <v>24</v>
       </c>
       <c r="B279" s="30" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D279" s="34">
         <v>1021.12</v>
@@ -6309,7 +6326,7 @@
         <v>70</v>
       </c>
       <c r="B280" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D280" s="34">
         <v>869.15</v>
@@ -6331,7 +6348,7 @@
         <v>70</v>
       </c>
       <c r="B281" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D281" s="34">
         <v>921.15</v>
@@ -6345,7 +6362,7 @@
         <v>70</v>
       </c>
       <c r="B282" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D282" s="34">
         <v>971.15</v>
@@ -6359,7 +6376,7 @@
         <v>70</v>
       </c>
       <c r="B283" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D283" s="34">
         <v>1021.15</v>
@@ -6373,7 +6390,7 @@
         <v>70</v>
       </c>
       <c r="B284" s="30" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="D284" s="34">
         <v>1071.1500000000001</v>
@@ -6387,7 +6404,7 @@
         <v>25</v>
       </c>
       <c r="B285" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D285" s="34">
         <v>1127.6041666666599</v>
@@ -6404,7 +6421,7 @@
         <v>25</v>
       </c>
       <c r="B286" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D286" s="34">
         <v>1127.6041666666599</v>
@@ -6421,7 +6438,7 @@
         <v>25</v>
       </c>
       <c r="B287" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D287" s="34">
         <v>1127.6041666666599</v>
@@ -6438,7 +6455,7 @@
         <v>25</v>
       </c>
       <c r="B288" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D288" s="34">
         <v>1299.4791666666599</v>
@@ -6455,7 +6472,7 @@
         <v>25</v>
       </c>
       <c r="B289" s="30" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D289" s="34">
         <v>1299.4791666666599</v>
@@ -6472,7 +6489,7 @@
         <v>25</v>
       </c>
       <c r="B290" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D290" s="34">
         <v>1150.5208333333301</v>
@@ -6489,7 +6506,7 @@
         <v>25</v>
       </c>
       <c r="B291" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D291" s="34">
         <v>1151.0416666666599</v>
@@ -6506,7 +6523,7 @@
         <v>25</v>
       </c>
       <c r="B292" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D292" s="34">
         <v>1168.75</v>
@@ -6523,7 +6540,7 @@
         <v>25</v>
       </c>
       <c r="B293" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D293" s="34">
         <v>1193.2291666666599</v>
@@ -6540,7 +6557,7 @@
         <v>25</v>
       </c>
       <c r="B294" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D294" s="34">
         <v>1224.4791666666599</v>
@@ -6557,7 +6574,7 @@
         <v>25</v>
       </c>
       <c r="B295" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D295" s="34">
         <v>1207.2916666666599</v>
@@ -6571,7 +6588,7 @@
         <v>25</v>
       </c>
       <c r="B296" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D296" s="34">
         <v>1239.06249999999</v>
@@ -6585,7 +6602,7 @@
         <v>25</v>
       </c>
       <c r="B297" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D297" s="34">
         <v>1275.5208333333301</v>
@@ -6599,7 +6616,7 @@
         <v>25</v>
       </c>
       <c r="B298" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D298" s="34">
         <v>1314.06249999999</v>
@@ -6613,7 +6630,7 @@
         <v>25</v>
       </c>
       <c r="B299" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D299" s="34">
         <v>1371.875</v>
@@ -6627,7 +6644,7 @@
         <v>47</v>
       </c>
       <c r="B300" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D300" s="34">
         <v>979.73856209150301</v>
@@ -6641,7 +6658,7 @@
         <v>47</v>
       </c>
       <c r="B301" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D301" s="34">
         <v>1004.79302832244</v>
@@ -6655,7 +6672,7 @@
         <v>47</v>
       </c>
       <c r="B302" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D302" s="34">
         <v>1010.23965141612</v>
@@ -6669,7 +6686,7 @@
         <v>47</v>
       </c>
       <c r="B303" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D303" s="34">
         <v>1002.61437908496</v>
@@ -6683,7 +6700,7 @@
         <v>47</v>
       </c>
       <c r="B304" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D304" s="34">
         <v>980.827886710239</v>
@@ -6697,7 +6714,7 @@
         <v>47</v>
       </c>
       <c r="B305" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D305" s="34">
         <v>980.827886710239</v>
@@ -6711,7 +6728,7 @@
         <v>47</v>
       </c>
       <c r="B306" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D306" s="34">
         <v>965.57734204792996</v>
@@ -6725,7 +6742,7 @@
         <v>47</v>
       </c>
       <c r="B307" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D307" s="34">
         <v>1124.6187363834399</v>
@@ -6739,7 +6756,7 @@
         <v>47</v>
       </c>
       <c r="B308" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D308" s="34">
         <v>1124.6187363834399</v>
@@ -6753,7 +6770,7 @@
         <v>47</v>
       </c>
       <c r="B309" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D309" s="34">
         <v>1210.67538126361</v>
@@ -6767,7 +6784,7 @@
         <v>47</v>
       </c>
       <c r="B310" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D310" s="34">
         <v>1242.2657952069701</v>
@@ -6781,7 +6798,7 @@
         <v>47</v>
       </c>
       <c r="B311" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D311" s="34">
         <v>1244.44444444444</v>
@@ -6795,7 +6812,7 @@
         <v>47</v>
       </c>
       <c r="B312" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D312" s="34">
         <v>1282.5708061002099</v>
@@ -6809,7 +6826,7 @@
         <v>47</v>
       </c>
       <c r="B313" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D313" s="34">
         <v>1274.9455337690599</v>
@@ -6823,7 +6840,7 @@
         <v>47</v>
       </c>
       <c r="B314" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D314" s="34">
         <v>1277.1241830065301</v>
@@ -6837,7 +6854,7 @@
         <v>47</v>
       </c>
       <c r="B315" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D315" s="34">
         <v>1277.1241830065301</v>
@@ -6851,7 +6868,7 @@
         <v>47</v>
       </c>
       <c r="B316" s="30" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D316" s="34">
         <v>1320.69716775599</v>
@@ -6865,7 +6882,7 @@
         <v>48</v>
       </c>
       <c r="B317" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D317" s="34">
         <v>907.84313725490199</v>
@@ -6879,7 +6896,7 @@
         <v>48</v>
       </c>
       <c r="B318" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D318" s="34">
         <v>942.70152505446595</v>
@@ -6893,7 +6910,7 @@
         <v>48</v>
       </c>
       <c r="B319" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D319" s="34">
         <v>978.649237472766</v>
@@ -6907,7 +6924,7 @@
         <v>48</v>
       </c>
       <c r="B320" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D320" s="34">
         <v>1006.9716775599099</v>
@@ -6921,7 +6938,7 @@
         <v>48</v>
       </c>
       <c r="B321" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D321" s="34">
         <v>1034.20479302832</v>
@@ -6935,7 +6952,7 @@
         <v>48</v>
       </c>
       <c r="B322" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D322" s="34">
         <v>1087.5816993464</v>
@@ -7425,7 +7442,7 @@
         <v>27</v>
       </c>
       <c r="B351" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D351" s="34">
         <v>1197.57645701096</v>
@@ -7439,7 +7456,7 @@
         <v>27</v>
       </c>
       <c r="B352" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D352" s="34">
         <v>1197.57645701096</v>
@@ -7453,7 +7470,7 @@
         <v>27</v>
       </c>
       <c r="B353" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D353" s="34">
         <v>1160.6462781304001</v>
@@ -7467,7 +7484,7 @@
         <v>27</v>
       </c>
       <c r="B354" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D354" s="34">
         <v>1160.6462781304001</v>
@@ -7481,7 +7498,7 @@
         <v>27</v>
       </c>
       <c r="B355" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D355" s="34">
         <v>1131.5637622619699</v>
@@ -7495,7 +7512,7 @@
         <v>27</v>
       </c>
       <c r="B356" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D356" s="34">
         <v>1132.0253894979801</v>
@@ -7509,7 +7526,7 @@
         <v>27</v>
       </c>
       <c r="B357" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D357" s="34">
         <v>1102.0196191575301</v>
@@ -7523,7 +7540,7 @@
         <v>27</v>
       </c>
       <c r="B358" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D358" s="34">
         <v>1090.9405654933601</v>
@@ -7537,7 +7554,7 @@
         <v>27</v>
       </c>
       <c r="B359" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D359" s="34">
         <v>1090.01731102135</v>
@@ -7551,7 +7568,7 @@
         <v>27</v>
       </c>
       <c r="B360" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D360" s="34">
         <v>1097.8649740334599</v>
@@ -7565,7 +7582,7 @@
         <v>27</v>
       </c>
       <c r="B361" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D361" s="34">
         <v>1052.1638776687801</v>
@@ -7579,7 +7596,7 @@
         <v>27</v>
       </c>
       <c r="B362" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D362" s="34">
         <v>1056.7801500288499</v>
@@ -7593,7 +7610,7 @@
         <v>27</v>
       </c>
       <c r="B363" s="30" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D363" s="34">
         <v>1052.1638776687801</v>
@@ -7607,7 +7624,7 @@
         <v>28</v>
       </c>
       <c r="B364" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D364" s="34">
         <v>1077.55337564916</v>
@@ -7621,7 +7638,7 @@
         <v>28</v>
       </c>
       <c r="B365" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D365" s="34">
         <v>1147.72071552221</v>
@@ -7635,7 +7652,7 @@
         <v>28</v>
       </c>
       <c r="B366" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D366" s="34">
         <v>1204.96249278707</v>
@@ -7649,7 +7666,7 @@
         <v>28</v>
       </c>
       <c r="B367" s="30" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="D367" s="34">
         <v>1301.9042123485201</v>
@@ -7663,7 +7680,7 @@
         <v>29</v>
       </c>
       <c r="B368" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D368" s="34">
         <v>1301.9042123485201</v>
@@ -7677,7 +7694,7 @@
         <v>29</v>
       </c>
       <c r="B369" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D369" s="34">
         <v>1204.96249278707</v>
@@ -7691,7 +7708,7 @@
         <v>29</v>
       </c>
       <c r="B370" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D370" s="34">
         <v>1146.7974610501999</v>
@@ -7705,7 +7722,7 @@
         <v>29</v>
       </c>
       <c r="B371" s="30" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="D371" s="34">
         <v>1076.6301211771399</v>
@@ -7719,7 +7736,7 @@
         <v>30</v>
       </c>
       <c r="B372" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D372" s="34">
         <v>1052.1638776687801</v>
@@ -7733,7 +7750,7 @@
         <v>30</v>
       </c>
       <c r="B373" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D373" s="34">
         <v>1089.0940565493299</v>
@@ -7747,7 +7764,7 @@
         <v>30</v>
       </c>
       <c r="B374" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D374" s="34">
         <v>1117.71494518176</v>
@@ -7761,7 +7778,7 @@
         <v>30</v>
       </c>
       <c r="B375" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D375" s="34">
         <v>1127.40911713791</v>
@@ -7775,7 +7792,7 @@
         <v>30</v>
       </c>
       <c r="B376" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D376" s="34">
         <v>1157.41488747836</v>
@@ -7789,7 +7806,7 @@
         <v>31</v>
       </c>
       <c r="B377" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D377" s="34">
         <v>1057.24177726485</v>
@@ -7803,7 +7820,7 @@
         <v>31</v>
       </c>
       <c r="B378" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D378" s="34">
         <v>1108.0207732256199</v>
@@ -7817,7 +7834,7 @@
         <v>31</v>
       </c>
       <c r="B379" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D379" s="34">
         <v>1162.0311598384301</v>
@@ -7831,7 +7848,7 @@
         <v>31</v>
       </c>
       <c r="B380" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D380" s="34">
         <v>1149.1055972302299</v>
@@ -7845,7 +7862,7 @@
         <v>31</v>
       </c>
       <c r="B381" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D381" s="34">
         <v>1192.49855741488</v>
@@ -7859,7 +7876,7 @@
         <v>32</v>
       </c>
       <c r="B382" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D382" s="34">
         <v>1054.01038661281</v>
@@ -7873,7 +7890,7 @@
         <v>32</v>
       </c>
       <c r="B383" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D383" s="34">
         <v>1061.8580496249201</v>
@@ -7887,7 +7904,7 @@
         <v>32</v>
       </c>
       <c r="B384" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D384" s="34">
         <v>1066.9359492210001</v>
@@ -7901,7 +7918,7 @@
         <v>32</v>
       </c>
       <c r="B385" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D385" s="34">
         <v>1072.9371032890899</v>
@@ -7915,7 +7932,7 @@
         <v>32</v>
       </c>
       <c r="B386" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D386" s="34">
         <v>1082.63127524523</v>
@@ -7929,7 +7946,7 @@
         <v>32</v>
       </c>
       <c r="B387" s="30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D387" s="34">
         <v>1092.32544720138</v>
@@ -7943,7 +7960,7 @@
         <v>33</v>
       </c>
       <c r="B388" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D388" s="32">
         <v>1056</v>
@@ -7957,7 +7974,7 @@
         <v>33</v>
       </c>
       <c r="B389" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D389" s="32">
         <v>1057</v>
@@ -7971,7 +7988,7 @@
         <v>33</v>
       </c>
       <c r="B390" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D390" s="32">
         <v>1057</v>
@@ -7985,7 +8002,7 @@
         <v>33</v>
       </c>
       <c r="B391" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D391" s="32">
         <v>1057</v>
@@ -7999,7 +8016,7 @@
         <v>33</v>
       </c>
       <c r="B392" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D392" s="32">
         <v>1058</v>
@@ -8013,7 +8030,7 @@
         <v>33</v>
       </c>
       <c r="B393" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D393" s="32">
         <v>1091</v>
@@ -8027,7 +8044,7 @@
         <v>33</v>
       </c>
       <c r="B394" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D394" s="32">
         <v>1091</v>
@@ -8041,7 +8058,7 @@
         <v>33</v>
       </c>
       <c r="B395" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D395" s="32">
         <v>1091</v>
@@ -8055,7 +8072,7 @@
         <v>33</v>
       </c>
       <c r="B396" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D396" s="32">
         <v>1091</v>
@@ -8069,7 +8086,7 @@
         <v>33</v>
       </c>
       <c r="B397" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D397" s="32">
         <v>1104</v>
@@ -8083,7 +8100,7 @@
         <v>33</v>
       </c>
       <c r="B398" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D398" s="32">
         <v>1104</v>
@@ -8097,7 +8114,7 @@
         <v>33</v>
       </c>
       <c r="B399" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D399" s="32">
         <v>1106</v>
@@ -8111,7 +8128,7 @@
         <v>33</v>
       </c>
       <c r="B400" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D400" s="32">
         <v>1106</v>
@@ -8125,7 +8142,7 @@
         <v>33</v>
       </c>
       <c r="B401" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D401" s="32">
         <v>1108</v>
@@ -8139,7 +8156,7 @@
         <v>33</v>
       </c>
       <c r="B402" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D402" s="32">
         <v>1150</v>
@@ -8153,7 +8170,7 @@
         <v>33</v>
       </c>
       <c r="B403" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D403" s="32">
         <v>1151</v>
@@ -8167,7 +8184,7 @@
         <v>33</v>
       </c>
       <c r="B404" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D404" s="32">
         <v>1152</v>
@@ -8181,7 +8198,7 @@
         <v>33</v>
       </c>
       <c r="B405" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D405" s="32">
         <v>1152</v>
@@ -8195,7 +8212,7 @@
         <v>33</v>
       </c>
       <c r="B406" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D406" s="32">
         <v>1155</v>
@@ -8209,7 +8226,7 @@
         <v>33</v>
       </c>
       <c r="B407" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D407" s="32">
         <v>1157</v>
@@ -8223,7 +8240,7 @@
         <v>33</v>
       </c>
       <c r="B408" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D408" s="32">
         <v>1159</v>
@@ -8237,7 +8254,7 @@
         <v>33</v>
       </c>
       <c r="B409" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D409" s="32">
         <v>1160</v>
@@ -8251,7 +8268,7 @@
         <v>33</v>
       </c>
       <c r="B410" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D410" s="32">
         <v>1161</v>
@@ -8265,7 +8282,7 @@
         <v>33</v>
       </c>
       <c r="B411" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D411" s="32">
         <v>1162</v>
@@ -8279,7 +8296,7 @@
         <v>33</v>
       </c>
       <c r="B412" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D412" s="32">
         <v>1189</v>
@@ -8293,7 +8310,7 @@
         <v>33</v>
       </c>
       <c r="B413" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D413" s="32">
         <v>1190</v>
@@ -8307,7 +8324,7 @@
         <v>33</v>
       </c>
       <c r="B414" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D414" s="32">
         <v>1190</v>
@@ -8321,7 +8338,7 @@
         <v>33</v>
       </c>
       <c r="B415" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D415" s="32">
         <v>1191</v>
@@ -8335,7 +8352,7 @@
         <v>33</v>
       </c>
       <c r="B416" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D416" s="32">
         <v>1192</v>
@@ -8349,7 +8366,7 @@
         <v>33</v>
       </c>
       <c r="B417" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D417" s="32">
         <v>1196</v>
@@ -8363,7 +8380,7 @@
         <v>33</v>
       </c>
       <c r="B418" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D418" s="32">
         <v>1197</v>
@@ -8377,7 +8394,7 @@
         <v>33</v>
       </c>
       <c r="B419" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D419" s="32">
         <v>1198</v>
@@ -8391,7 +8408,7 @@
         <v>33</v>
       </c>
       <c r="B420" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D420" s="32">
         <v>1198</v>
@@ -8405,7 +8422,7 @@
         <v>33</v>
       </c>
       <c r="B421" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D421" s="32">
         <v>1199</v>
@@ -8419,7 +8436,7 @@
         <v>33</v>
       </c>
       <c r="B422" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D422" s="32">
         <v>1245</v>
@@ -8433,7 +8450,7 @@
         <v>33</v>
       </c>
       <c r="B423" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D423" s="32">
         <v>1245</v>
@@ -8447,7 +8464,7 @@
         <v>33</v>
       </c>
       <c r="B424" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D424" s="32">
         <v>1246</v>
@@ -8461,7 +8478,7 @@
         <v>33</v>
       </c>
       <c r="B425" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D425" s="32">
         <v>1247</v>
@@ -8475,7 +8492,7 @@
         <v>33</v>
       </c>
       <c r="B426" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D426" s="32">
         <v>1249</v>
@@ -8489,7 +8506,7 @@
         <v>33</v>
       </c>
       <c r="B427" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D427" s="32">
         <v>1289</v>
@@ -8503,7 +8520,7 @@
         <v>33</v>
       </c>
       <c r="B428" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D428" s="32">
         <v>1291</v>
@@ -8517,7 +8534,7 @@
         <v>33</v>
       </c>
       <c r="B429" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D429" s="32">
         <v>1291</v>
@@ -8531,7 +8548,7 @@
         <v>33</v>
       </c>
       <c r="B430" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D430" s="32">
         <v>1297</v>
@@ -8545,7 +8562,7 @@
         <v>33</v>
       </c>
       <c r="B431" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D431" s="32">
         <v>1331</v>
@@ -8559,7 +8576,7 @@
         <v>33</v>
       </c>
       <c r="B432" s="30" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="D432" s="32">
         <v>1335</v>
@@ -8573,7 +8590,7 @@
         <v>49</v>
       </c>
       <c r="B433" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D433" s="32">
         <v>986.86210640607999</v>
@@ -8587,7 +8604,7 @@
         <v>49</v>
       </c>
       <c r="B434" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D434" s="32">
         <v>1014.65798045602</v>
@@ -8601,7 +8618,7 @@
         <v>49</v>
       </c>
       <c r="B435" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D435" s="32">
         <v>1019.86970684039</v>
@@ -8615,7 +8632,7 @@
         <v>49</v>
       </c>
       <c r="B436" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D436" s="32">
         <v>1038.1107491856601</v>
@@ -8629,7 +8646,7 @@
         <v>49</v>
       </c>
       <c r="B437" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D437" s="32">
         <v>1056.3517915309401</v>
@@ -8643,7 +8660,7 @@
         <v>49</v>
       </c>
       <c r="B438" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D438" s="32">
         <v>1077.1986970684</v>
@@ -8657,7 +8674,7 @@
         <v>49</v>
       </c>
       <c r="B439" s="30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D439" s="32">
         <v>1093.70249728555</v>
@@ -8671,7 +8688,7 @@
         <v>50</v>
       </c>
       <c r="B440" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D440" s="32">
         <v>986.86210640607999</v>
@@ -8685,7 +8702,7 @@
         <v>50</v>
       </c>
       <c r="B441" s="30" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D441" s="32">
         <v>1169.27252985884</v>
@@ -8699,7 +8716,7 @@
         <v>34</v>
       </c>
       <c r="B442" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C442" s="3"/>
       <c r="D442" s="34">
@@ -8714,7 +8731,7 @@
         <v>34</v>
       </c>
       <c r="B443" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D443" s="32">
         <v>1223.4123532099288</v>
@@ -8728,7 +8745,7 @@
         <v>34</v>
       </c>
       <c r="B444" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D444" s="32">
         <v>1236.3180170442961</v>
@@ -8742,7 +8759,7 @@
         <v>34</v>
       </c>
       <c r="B445" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D445" s="32">
         <v>1239.9574007388751</v>
@@ -8756,7 +8773,7 @@
         <v>34</v>
       </c>
       <c r="B446" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D446" s="32">
         <v>1256.7239583535199</v>
@@ -8770,7 +8787,7 @@
         <v>34</v>
       </c>
       <c r="B447" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D447" s="34">
         <v>1265.7552216950689</v>
@@ -8784,7 +8801,7 @@
         <v>34</v>
       </c>
       <c r="B448" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D448" s="32">
         <v>1276.11284420829</v>
@@ -8798,7 +8815,7 @@
         <v>34</v>
       </c>
       <c r="B449" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D449" s="34">
         <v>1346.8049516489</v>
@@ -8812,7 +8829,7 @@
         <v>34</v>
       </c>
       <c r="B450" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D450" s="34">
         <v>1339.5174048965901</v>
@@ -8826,7 +8843,7 @@
         <v>34</v>
       </c>
       <c r="B451" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D451" s="34">
         <v>1358.9434342108498</v>
@@ -8840,7 +8857,7 @@
         <v>34</v>
       </c>
       <c r="B452" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D452" s="34">
         <v>1340.9383110560598</v>
@@ -8854,7 +8871,7 @@
         <v>34</v>
       </c>
       <c r="B453" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D453" s="34">
         <v>1350.0506146728699</v>
@@ -8868,7 +8885,7 @@
         <v>34</v>
       </c>
       <c r="B454" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D454" s="34">
         <v>1358.7388075158301</v>
@@ -8882,7 +8899,7 @@
         <v>34</v>
       </c>
       <c r="B455" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D455" s="1">
         <v>1371.21698389823</v>
@@ -8896,7 +8913,7 @@
         <v>34</v>
       </c>
       <c r="B456" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D456" s="1">
         <v>1384.5467585064298</v>
@@ -8910,7 +8927,7 @@
         <v>34</v>
       </c>
       <c r="B457" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D457" s="1">
         <v>1395.27108826519</v>
@@ -8924,7 +8941,7 @@
         <v>34</v>
       </c>
       <c r="B458" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D458" s="1">
         <v>1407.2339835640901</v>
@@ -8938,7 +8955,7 @@
         <v>34</v>
       </c>
       <c r="B459" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D459" s="1">
         <v>1412.94327095581</v>
@@ -8952,7 +8969,7 @@
         <v>34</v>
       </c>
       <c r="B460" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D460" s="1">
         <v>1428.4948997772499</v>
@@ -8966,7 +8983,7 @@
         <v>34</v>
       </c>
       <c r="B461" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D461" s="1">
         <v>1428.8481003102402</v>
@@ -8980,7 +8997,7 @@
         <v>34</v>
       </c>
       <c r="B462" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D462" s="1">
         <v>1440.9663228033801</v>
@@ -8994,7 +9011,7 @@
         <v>34</v>
       </c>
       <c r="B463" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D463" s="1">
         <v>1440.8683991374401</v>
@@ -9008,7 +9025,7 @@
         <v>34</v>
       </c>
       <c r="B464" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D464" s="1">
         <v>1454.2386938832701</v>
@@ -9022,7 +9039,7 @@
         <v>34</v>
       </c>
       <c r="B465" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D465" s="1">
         <v>1454.5952710943998</v>
@@ -9036,7 +9053,7 @@
         <v>34</v>
       </c>
       <c r="B466" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D466" s="1">
         <v>1470.1907967316101</v>
@@ -9050,7 +9067,7 @@
         <v>34</v>
       </c>
       <c r="B467" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D467" s="1">
         <v>1458.1738745825301</v>
@@ -9064,7 +9081,7 @@
         <v>34</v>
       </c>
       <c r="B468" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D468" s="1">
         <v>1459.96824134381</v>
@@ -9078,7 +9095,7 @@
         <v>34</v>
       </c>
       <c r="B469" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D469" s="1">
         <v>1448.40582007179</v>
@@ -9092,7 +9109,7 @@
         <v>34</v>
       </c>
       <c r="B470" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D470" s="1">
         <v>1557.4434844205898</v>
@@ -9106,7 +9123,7 @@
         <v>34</v>
       </c>
       <c r="B471" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D471" s="1">
         <v>1569.4536532133898</v>
@@ -9120,7 +9137,7 @@
         <v>34</v>
       </c>
       <c r="B472" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D472" s="1">
         <v>1577.2801177961499</v>
@@ -9134,7 +9151,7 @@
         <v>34</v>
       </c>
       <c r="B473" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D473" s="1">
         <v>1579.7977690140699</v>
@@ -9148,7 +9165,7 @@
         <v>34</v>
       </c>
       <c r="B474" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D474" s="1">
         <v>1581.45369197178</v>
@@ -9162,7 +9179,7 @@
         <v>34</v>
       </c>
       <c r="B475" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D475" s="1">
         <v>1590.9934830405598</v>
@@ -9176,7 +9193,7 @@
         <v>34</v>
       </c>
       <c r="B476" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D476" s="1">
         <v>1597.06610099967</v>
@@ -9190,7 +9207,7 @@
         <v>34</v>
       </c>
       <c r="B477" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D477" s="1">
         <v>1604.7304850319199</v>
@@ -9204,7 +9221,7 @@
         <v>34</v>
       </c>
       <c r="B478" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D478" s="1">
         <v>1627.4663342547199</v>
@@ -9218,7 +9235,7 @@
         <v>34</v>
       </c>
       <c r="B479" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D479" s="1">
         <v>1644.7616796653999</v>
@@ -9232,7 +9249,7 @@
         <v>34</v>
       </c>
       <c r="B480" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D480" s="1">
         <v>1663.7129480338001</v>
@@ -9246,7 +9263,7 @@
         <v>34</v>
       </c>
       <c r="B481" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D481" s="1">
         <v>1736.6188056601302</v>
@@ -9260,7 +9277,7 @@
         <v>34</v>
       </c>
       <c r="B482" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D482" s="1">
         <v>1732.0380041013398</v>
@@ -9274,7 +9291,7 @@
         <v>34</v>
       </c>
       <c r="B483" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D483" s="1">
         <v>1751.0432993198999</v>
@@ -9288,7 +9305,7 @@
         <v>34</v>
       </c>
       <c r="B484" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D484" s="1">
         <v>1760.4480232632498</v>
@@ -9302,7 +9319,7 @@
         <v>34</v>
       </c>
       <c r="B485" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D485" s="1">
         <v>1973.8878482162602</v>
@@ -9316,7 +9333,7 @@
         <v>34</v>
       </c>
       <c r="B486" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D486" s="1">
         <v>1984.57503451552</v>
@@ -9330,7 +9347,7 @@
         <v>34</v>
       </c>
       <c r="B487" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D487" s="1">
         <v>1992.67703603414</v>
@@ -9344,7 +9361,7 @@
         <v>34</v>
       </c>
       <c r="B488" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D488" s="1">
         <v>1994.77395315637</v>
@@ -9358,7 +9375,7 @@
         <v>34</v>
       </c>
       <c r="B489" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D489" s="1">
         <v>1996.8472335316399</v>
@@ -9372,7 +9389,7 @@
         <v>34</v>
       </c>
       <c r="B490" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D490" s="1">
         <v>2005.6097132936</v>
@@ -9386,7 +9403,7 @@
         <v>34</v>
       </c>
       <c r="B491" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D491" s="1">
         <v>2019.4412622727498</v>
@@ -9400,7 +9417,7 @@
         <v>34</v>
       </c>
       <c r="B492" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D492" s="1">
         <v>2209.04376559511</v>
@@ -9414,7 +9431,7 @@
         <v>34</v>
       </c>
       <c r="B493" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D493" s="1">
         <v>2225.8609733817902</v>
@@ -9428,7 +9445,7 @@
         <v>34</v>
       </c>
       <c r="B494" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D494" s="1">
         <v>2220.7817741301797</v>
@@ -9442,7 +9459,7 @@
         <v>34</v>
       </c>
       <c r="B495" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D495" s="1">
         <v>2233.7786082742095</v>
@@ -9456,7 +9473,7 @@
         <v>34</v>
       </c>
       <c r="B496" s="30" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D496" s="1">
         <v>2243.17995553942</v>
@@ -9465,7 +9482,7 @@
         <v>1.57558767412648</v>
       </c>
       <c r="J496" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="497" spans="1:10" x14ac:dyDescent="0.25">
@@ -9473,7 +9490,7 @@
         <v>35</v>
       </c>
       <c r="B497" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D497" s="1">
         <v>1151.0185516430699</v>
@@ -9490,7 +9507,7 @@
         <v>35</v>
       </c>
       <c r="B498" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D498" s="1">
         <v>1151.4524454438499</v>
@@ -9507,7 +9524,7 @@
         <v>35</v>
       </c>
       <c r="B499" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D499" s="1">
         <v>1169.93049522154</v>
@@ -9524,7 +9541,7 @@
         <v>35</v>
       </c>
       <c r="B500" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D500" s="1">
         <v>1194.7866305514301</v>
@@ -9541,7 +9558,7 @@
         <v>35</v>
       </c>
       <c r="B501" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D501" s="1">
         <v>1239.1552103030599</v>
@@ -9558,7 +9575,7 @@
         <v>35</v>
       </c>
       <c r="B502" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D502" s="1">
         <v>1207.8627280625501</v>
@@ -9575,7 +9592,7 @@
         <v>35</v>
       </c>
       <c r="B503" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D503" s="1">
         <v>1225.69888076864</v>
@@ -9592,7 +9609,7 @@
         <v>35</v>
       </c>
       <c r="B504" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D504" s="1">
         <v>1276.5620687892799</v>
@@ -9609,7 +9626,7 @@
         <v>35</v>
       </c>
       <c r="B505" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D505" s="1">
         <v>1314.06909592681</v>
@@ -9626,7 +9643,7 @@
         <v>35</v>
       </c>
       <c r="B506" s="30" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D506" s="1">
         <v>1372.22721929779</v>
@@ -9643,7 +9660,7 @@
         <v>36</v>
       </c>
       <c r="B507" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D507" s="1">
         <v>1135.3949129852699</v>
@@ -9657,7 +9674,7 @@
         <v>36</v>
       </c>
       <c r="B508" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D508" s="1">
         <v>1131.7135207496599</v>
@@ -9671,7 +9688,7 @@
         <v>36</v>
       </c>
       <c r="B509" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D509" s="1">
         <v>1182.2489959839299</v>
@@ -9685,7 +9702,7 @@
         <v>36</v>
       </c>
       <c r="B510" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D510" s="1">
         <v>1160.8299866131099</v>
@@ -9699,7 +9716,7 @@
         <v>36</v>
       </c>
       <c r="B511" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D511" s="1">
         <v>1149.11646586345</v>
@@ -9713,7 +9730,7 @@
         <v>36</v>
       </c>
       <c r="B512" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D512" s="1">
         <v>1155.1405622489899</v>
@@ -9727,7 +9744,7 @@
         <v>36</v>
       </c>
       <c r="B513" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D513" s="1">
         <v>1162.8380187416301</v>
@@ -9741,7 +9758,7 @@
         <v>36</v>
       </c>
       <c r="B514" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D514" s="1">
         <v>1188.2730923694701</v>
@@ -9755,7 +9772,7 @@
         <v>36</v>
       </c>
       <c r="B515" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D515" s="1">
         <v>1192.2891566265</v>
@@ -9769,7 +9786,7 @@
         <v>36</v>
       </c>
       <c r="B516" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D516" s="1">
         <v>1209.6921017402899</v>
@@ -9783,7 +9800,7 @@
         <v>36</v>
       </c>
       <c r="B517" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D517" s="1">
         <v>1215.71619812583</v>
@@ -9797,7 +9814,7 @@
         <v>36</v>
       </c>
       <c r="B518" s="30" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D518" s="1">
         <v>1233.1191432396199</v>
@@ -9811,7 +9828,7 @@
         <v>37</v>
       </c>
       <c r="B519" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D519" s="1">
         <v>1184.5917001338601</v>
@@ -9825,7 +9842,7 @@
         <v>37</v>
       </c>
       <c r="B520" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D520" s="1">
         <v>1201.3253012048101</v>
@@ -9839,7 +9856,7 @@
         <v>37</v>
       </c>
       <c r="B521" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D521" s="1">
         <v>1207.6840696117799</v>
@@ -9853,7 +9870,7 @@
         <v>37</v>
       </c>
       <c r="B522" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D522" s="1">
         <v>1225.08701472556</v>
@@ -9867,7 +9884,7 @@
         <v>37</v>
       </c>
       <c r="B523" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D523" s="1">
         <v>1223.7483266398899</v>
@@ -9881,7 +9898,7 @@
         <v>37</v>
       </c>
       <c r="B524" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D524" s="1">
         <v>1242.4899598393499</v>
@@ -9895,7 +9912,7 @@
         <v>37</v>
       </c>
       <c r="B525" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D525" s="1">
         <v>1250.52208835341</v>
@@ -9909,7 +9926,7 @@
         <v>37</v>
       </c>
       <c r="B526" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D526" s="1">
         <v>1295.3681392235601</v>
@@ -9923,7 +9940,7 @@
         <v>37</v>
       </c>
       <c r="B527" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D527" s="1">
         <v>1287.6706827309199</v>
@@ -9937,7 +9954,7 @@
         <v>37</v>
       </c>
       <c r="B528" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D528" s="1">
         <v>1288.0053547523401</v>
@@ -9951,7 +9968,7 @@
         <v>37</v>
       </c>
       <c r="B529" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D529" s="1">
         <v>1328.50066934404</v>
@@ -9965,7 +9982,7 @@
         <v>37</v>
       </c>
       <c r="B530" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D530" s="1">
         <v>1352.26238286479</v>
@@ -9979,7 +9996,7 @@
         <v>37</v>
       </c>
       <c r="B531" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D531" s="1">
         <v>1359.9598393574199</v>
@@ -9993,7 +10010,7 @@
         <v>37</v>
       </c>
       <c r="B532" s="30" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D532" s="1">
         <v>1417.18875502008</v>
@@ -10007,7 +10024,7 @@
         <v>38</v>
       </c>
       <c r="B533" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D533">
         <v>1121.2</v>
@@ -10021,7 +10038,7 @@
         <v>38</v>
       </c>
       <c r="B534" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D534">
         <f t="shared" ref="D534:D539" si="0">D533+25</f>
@@ -10036,7 +10053,7 @@
         <v>38</v>
       </c>
       <c r="B535" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D535">
         <f t="shared" si="0"/>
@@ -10051,7 +10068,7 @@
         <v>38</v>
       </c>
       <c r="B536" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D536">
         <f t="shared" si="0"/>
@@ -10066,7 +10083,7 @@
         <v>38</v>
       </c>
       <c r="B537" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D537">
         <f t="shared" si="0"/>
@@ -10081,7 +10098,7 @@
         <v>38</v>
       </c>
       <c r="B538" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D538">
         <f t="shared" si="0"/>
@@ -10096,7 +10113,7 @@
         <v>38</v>
       </c>
       <c r="B539" s="30" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D539">
         <f t="shared" si="0"/>
@@ -10111,7 +10128,7 @@
         <v>39</v>
       </c>
       <c r="B540" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D540" s="1">
         <v>1276.21082621082</v>
@@ -10125,7 +10142,7 @@
         <v>39</v>
       </c>
       <c r="B541" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D541" s="1">
         <v>1292.5925925925901</v>
@@ -10139,7 +10156,7 @@
         <v>39</v>
       </c>
       <c r="B542" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D542" s="1">
         <v>1296.8660968660899</v>
@@ -10153,7 +10170,7 @@
         <v>39</v>
       </c>
       <c r="B543" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D543" s="1">
         <v>1314.6723646723599</v>
@@ -10167,7 +10184,7 @@
         <v>39</v>
       </c>
       <c r="B544" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D544" s="1">
         <v>1326.0683760683701</v>
@@ -10181,7 +10198,7 @@
         <v>39</v>
       </c>
       <c r="B545" s="30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="D545" s="1">
         <v>1346.7236467236401</v>
@@ -10195,7 +10212,7 @@
         <v>61</v>
       </c>
       <c r="B546" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D546" s="1">
         <v>1277.63532763532</v>
@@ -10209,7 +10226,7 @@
         <v>61</v>
       </c>
       <c r="B547" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D547" s="1">
         <v>1286.1823361823299</v>
@@ -10223,7 +10240,7 @@
         <v>61</v>
       </c>
       <c r="B548" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D548" s="1">
         <v>1298.29059829059</v>
@@ -10237,7 +10254,7 @@
         <v>61</v>
       </c>
       <c r="B549" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D549" s="1">
         <v>1321.79487179487</v>
@@ -10251,7 +10268,7 @@
         <v>61</v>
       </c>
       <c r="B550" s="30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D550" s="1">
         <v>1328.9173789173699</v>
@@ -10265,7 +10282,7 @@
         <v>40</v>
       </c>
       <c r="B551" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D551" s="1">
         <v>1130.5970149253701</v>
@@ -10279,7 +10296,7 @@
         <v>40</v>
       </c>
       <c r="B552" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D552" s="1">
         <v>1159.7014925373101</v>
@@ -10293,7 +10310,7 @@
         <v>40</v>
       </c>
       <c r="B553" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D553" s="1">
         <v>1172.38805970149</v>
@@ -10307,7 +10324,7 @@
         <v>40</v>
       </c>
       <c r="B554" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D554" s="1">
         <v>1176.86567164179</v>
@@ -10321,7 +10338,7 @@
         <v>40</v>
       </c>
       <c r="B555" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D555" s="1">
         <v>1197.76119402985</v>
@@ -10335,7 +10352,7 @@
         <v>40</v>
       </c>
       <c r="B556" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D556" s="1">
         <v>1207.4626865671601</v>
@@ -10349,7 +10366,7 @@
         <v>40</v>
       </c>
       <c r="B557" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D557" s="1">
         <v>1219.4029850746199</v>
@@ -10363,7 +10380,7 @@
         <v>40</v>
       </c>
       <c r="B558" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D558" s="1">
         <v>1243.28358208955</v>
@@ -10377,7 +10394,7 @@
         <v>40</v>
       </c>
       <c r="B559" s="30" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D559" s="1">
         <v>1262.6865671641699</v>
@@ -10391,7 +10408,7 @@
         <v>46</v>
       </c>
       <c r="B560" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D560" s="1">
         <v>1175.6070640176599</v>
@@ -10405,7 +10422,7 @@
         <v>46</v>
       </c>
       <c r="B561" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D561" s="1">
         <v>1197.6821192052901</v>
@@ -10419,7 +10436,7 @@
         <v>46</v>
       </c>
       <c r="B562" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D562" s="1">
         <v>1231.3465783664401</v>
@@ -10433,7 +10450,7 @@
         <v>46</v>
       </c>
       <c r="B563" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D563" s="1">
         <v>1264.4591611479</v>
@@ -10447,7 +10464,7 @@
         <v>46</v>
       </c>
       <c r="B564" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D564" s="1">
         <v>1283.2229580573901</v>
@@ -10461,7 +10478,7 @@
         <v>46</v>
       </c>
       <c r="B565" s="30" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="D565" s="1">
         <v>1299.2273730684301</v>
@@ -10475,7 +10492,7 @@
         <v>41</v>
       </c>
       <c r="B566" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D566" s="1">
         <v>1554.2416452442101</v>
@@ -10489,7 +10506,7 @@
         <v>41</v>
       </c>
       <c r="B567" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D567" s="1">
         <v>1564.5244215938301</v>
@@ -10503,7 +10520,7 @@
         <v>41</v>
       </c>
       <c r="B568" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D568" s="1">
         <v>1567.09511568123</v>
@@ -10517,7 +10534,7 @@
         <v>41</v>
       </c>
       <c r="B569" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D569" s="1">
         <v>1604.37017994858</v>
@@ -10531,7 +10548,7 @@
         <v>41</v>
       </c>
       <c r="B570" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D570" s="1">
         <v>1630.0771208226199</v>
@@ -10545,7 +10562,7 @@
         <v>41</v>
       </c>
       <c r="B571" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D571" s="1">
         <v>1736.76092544987</v>
@@ -10559,7 +10576,7 @@
         <v>41</v>
       </c>
       <c r="B572" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D572" s="1">
         <v>1716.19537275064</v>
@@ -10573,7 +10590,7 @@
         <v>41</v>
       </c>
       <c r="B573" s="30" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D573" s="1">
         <v>1703.34190231362</v>
@@ -10587,7 +10604,7 @@
         <v>42</v>
       </c>
       <c r="B574" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D574" s="1">
         <v>1578.6632390745499</v>
@@ -10601,7 +10618,7 @@
         <v>42</v>
       </c>
       <c r="B575" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D575" s="1">
         <v>1613.3676092544899</v>
@@ -10615,7 +10632,7 @@
         <v>42</v>
       </c>
       <c r="B576" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D576" s="1">
         <v>1614.6529562982</v>
@@ -10629,7 +10646,7 @@
         <v>42</v>
       </c>
       <c r="B577" s="30" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D577" s="1">
         <v>1586.37532133676</v>
@@ -10643,7 +10660,7 @@
         <v>43</v>
       </c>
       <c r="B578" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D578" s="1">
         <v>1712.3789020452</v>
@@ -10657,7 +10674,7 @@
         <v>43</v>
       </c>
       <c r="B579" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D579" s="1">
         <v>1730.7857911732999</v>
@@ -10671,7 +10688,7 @@
         <v>43</v>
       </c>
       <c r="B580" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D580" s="1">
         <v>1723.03552206673</v>
@@ -10685,7 +10702,7 @@
         <v>43</v>
       </c>
       <c r="B581" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D581" s="1">
         <v>1751.1302475780401</v>
@@ -10699,7 +10716,7 @@
         <v>43</v>
       </c>
       <c r="B582" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D582" s="1">
         <v>1768.56835306781</v>
@@ -10713,7 +10730,7 @@
         <v>43</v>
       </c>
       <c r="B583" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D583" s="1">
         <v>1794.7255113024701</v>
@@ -10727,7 +10744,7 @@
         <v>43</v>
       </c>
       <c r="B584" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D584" s="1">
         <v>1823.78902045209</v>
@@ -10741,7 +10758,7 @@
         <v>43</v>
       </c>
       <c r="B585" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D585" s="1">
         <v>1845.1022604951499</v>
@@ -10755,7 +10772,7 @@
         <v>43</v>
       </c>
       <c r="B586" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D586" s="1">
         <v>1872.22820236813</v>
@@ -10769,7 +10786,7 @@
         <v>43</v>
       </c>
       <c r="B587" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D587" s="1">
         <v>1872.22820236813</v>
@@ -10783,7 +10800,7 @@
         <v>43</v>
       </c>
       <c r="B588" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D588" s="1">
         <v>1816.03875134553</v>
@@ -10797,7 +10814,7 @@
         <v>43</v>
       </c>
       <c r="B589" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D589" s="1">
         <v>1776.3186221743799</v>
@@ -10811,7 +10828,7 @@
         <v>43</v>
       </c>
       <c r="B590" s="30" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D590" s="1">
         <v>1801.50699677072</v>
@@ -10825,7 +10842,7 @@
         <v>44</v>
       </c>
       <c r="B591" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D591" s="1">
         <v>1697.8471474703899</v>
@@ -10839,7 +10856,7 @@
         <v>44</v>
       </c>
       <c r="B592" s="30" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D592" s="1">
         <v>1841.2271259418701</v>
@@ -10853,7 +10870,7 @@
         <v>45</v>
       </c>
       <c r="B593" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D593" s="1">
         <v>1712.3789020452</v>
@@ -10867,7 +10884,7 @@
         <v>45</v>
       </c>
       <c r="B594" s="30" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D594" s="1">
         <v>1776.3186221743799</v>
@@ -10881,7 +10898,7 @@
         <v>100</v>
       </c>
       <c r="B595" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D595" s="1">
         <v>785.88122136744698</v>
@@ -10895,7 +10912,7 @@
         <v>100</v>
       </c>
       <c r="B596" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D596" s="1">
         <v>791.99994381536806</v>
@@ -10909,7 +10926,7 @@
         <v>100</v>
       </c>
       <c r="B597" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D597" s="1">
         <v>890.657995505229</v>
@@ -10923,7 +10940,7 @@
         <v>100</v>
       </c>
       <c r="B598" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D598" s="1">
         <v>924.23803699541804</v>
@@ -10937,7 +10954,7 @@
         <v>100</v>
       </c>
       <c r="B599" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D599" s="1">
         <v>964.97297519232404</v>
@@ -10951,7 +10968,7 @@
         <v>100</v>
       </c>
       <c r="B600" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D600" s="1">
         <v>973.5962356297</v>
@@ -10965,7 +10982,7 @@
         <v>100</v>
       </c>
       <c r="B601" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D601" s="1">
         <v>1043.36890396749</v>
@@ -10979,7 +10996,7 @@
         <v>100</v>
       </c>
       <c r="B602" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D602" s="1">
         <v>1049.4779021523</v>
@@ -10993,7 +11010,7 @@
         <v>100</v>
       </c>
       <c r="B603" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D603" s="1">
         <v>1049.49410925749</v>
@@ -11007,7 +11024,7 @@
         <v>100</v>
       </c>
       <c r="B604" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D604" s="1">
         <v>1056.08067680871</v>
@@ -11021,7 +11038,7 @@
         <v>100</v>
       </c>
       <c r="B605" s="30" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="D605" s="1">
         <v>1125.85226467283</v>
@@ -11035,7 +11052,7 @@
         <v>102</v>
       </c>
       <c r="B606" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D606" s="1">
         <v>811.82663583714998</v>
@@ -11049,7 +11066,7 @@
         <v>102</v>
       </c>
       <c r="B607" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D607" s="1">
         <v>815.39868182211001</v>
@@ -11063,7 +11080,7 @@
         <v>102</v>
       </c>
       <c r="B608" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D608" s="1">
         <v>855.58473938974805</v>
@@ -11077,7 +11094,7 @@
         <v>102</v>
       </c>
       <c r="B609" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D609" s="1">
         <v>888.66019967153602</v>
@@ -11091,7 +11108,7 @@
         <v>102</v>
       </c>
       <c r="B610" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D610" s="1">
         <v>945.15600743365803</v>
@@ -11105,7 +11122,7 @@
         <v>102</v>
       </c>
       <c r="B611" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D611" s="1">
         <v>1003.20337539977</v>
@@ -11119,7 +11136,7 @@
         <v>102</v>
       </c>
       <c r="B612" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D612" s="1">
         <v>1080.06611202351</v>
@@ -11133,7 +11150,7 @@
         <v>102</v>
       </c>
       <c r="B613" s="30" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="D613" s="1">
         <v>1141.6639165009899</v>
@@ -11147,7 +11164,7 @@
         <v>105</v>
       </c>
       <c r="B614" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D614" s="1">
         <v>1023</v>
@@ -11164,7 +11181,7 @@
         <v>105</v>
       </c>
       <c r="B615" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D615" s="1">
         <v>1023</v>
@@ -11178,7 +11195,7 @@
         <v>105</v>
       </c>
       <c r="B616" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D616" s="1">
         <v>1023</v>
@@ -11192,7 +11209,7 @@
         <v>105</v>
       </c>
       <c r="B617" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D617" s="1">
         <v>1048</v>
@@ -11206,7 +11223,7 @@
         <v>105</v>
       </c>
       <c r="B618" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D618" s="1">
         <v>1048</v>
@@ -11220,7 +11237,7 @@
         <v>105</v>
       </c>
       <c r="B619" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D619" s="1">
         <v>1073</v>
@@ -11234,7 +11251,7 @@
         <v>105</v>
       </c>
       <c r="B620" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D620" s="1">
         <v>1073</v>
@@ -11248,7 +11265,7 @@
         <v>105</v>
       </c>
       <c r="B621" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D621" s="1">
         <v>1073</v>
@@ -11262,7 +11279,7 @@
         <v>105</v>
       </c>
       <c r="B622" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D622" s="1">
         <v>1098</v>
@@ -11276,7 +11293,7 @@
         <v>105</v>
       </c>
       <c r="B623" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D623" s="1">
         <v>1098</v>
@@ -11290,7 +11307,7 @@
         <v>105</v>
       </c>
       <c r="B624" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D624" s="1">
         <v>1098</v>
@@ -11304,7 +11321,7 @@
         <v>105</v>
       </c>
       <c r="B625" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D625" s="1">
         <v>1123</v>
@@ -11318,7 +11335,7 @@
         <v>105</v>
       </c>
       <c r="B626" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D626" s="1">
         <v>1123</v>
@@ -11332,7 +11349,7 @@
         <v>105</v>
       </c>
       <c r="B627" s="30" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D627" s="1">
         <v>1123</v>
@@ -11346,7 +11363,7 @@
         <v>106</v>
       </c>
       <c r="B628" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D628" s="1">
         <v>1073</v>
@@ -11363,7 +11380,7 @@
         <v>106</v>
       </c>
       <c r="B629" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D629" s="1">
         <v>1073</v>
@@ -11377,7 +11394,7 @@
         <v>106</v>
       </c>
       <c r="B630" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D630" s="1">
         <v>1098</v>
@@ -11391,7 +11408,7 @@
         <v>106</v>
       </c>
       <c r="B631" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D631" s="1">
         <v>1098</v>
@@ -11405,7 +11422,7 @@
         <v>106</v>
       </c>
       <c r="B632" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D632" s="1">
         <v>1123</v>
@@ -11419,7 +11436,7 @@
         <v>106</v>
       </c>
       <c r="B633" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D633" s="1">
         <v>1123</v>
@@ -11433,7 +11450,7 @@
         <v>106</v>
       </c>
       <c r="B634" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D634" s="1">
         <v>1148</v>
@@ -11447,7 +11464,7 @@
         <v>106</v>
       </c>
       <c r="B635" s="30" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D635" s="1">
         <v>1173</v>
@@ -11461,7 +11478,7 @@
         <v>107</v>
       </c>
       <c r="B636" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D636" s="1">
         <v>1073</v>
@@ -11478,7 +11495,7 @@
         <v>107</v>
       </c>
       <c r="B637" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D637" s="1">
         <v>1073</v>
@@ -11492,7 +11509,7 @@
         <v>107</v>
       </c>
       <c r="B638" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D638" s="1">
         <v>1098</v>
@@ -11506,7 +11523,7 @@
         <v>107</v>
       </c>
       <c r="B639" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D639" s="1">
         <v>1098</v>
@@ -11520,7 +11537,7 @@
         <v>107</v>
       </c>
       <c r="B640" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D640" s="1">
         <v>1098</v>
@@ -11534,7 +11551,7 @@
         <v>107</v>
       </c>
       <c r="B641" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D641" s="1">
         <v>1123</v>
@@ -11548,7 +11565,7 @@
         <v>107</v>
       </c>
       <c r="B642" s="30" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D642" s="1">
         <v>1123</v>
@@ -11562,7 +11579,7 @@
         <v>208</v>
       </c>
       <c r="B643" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D643" s="1">
         <v>523.48130841121497</v>
@@ -11576,7 +11593,7 @@
         <v>208</v>
       </c>
       <c r="B644" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D644" s="1">
         <v>573.24766355140196</v>
@@ -11590,7 +11607,7 @@
         <v>208</v>
       </c>
       <c r="B645" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D645" s="1">
         <v>623.36448598130801</v>
@@ -11604,7 +11621,7 @@
         <v>208</v>
       </c>
       <c r="B646" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D646" s="1">
         <v>648.24766355140196</v>
@@ -11618,7 +11635,7 @@
         <v>208</v>
       </c>
       <c r="B647" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D647" s="1">
         <v>673.130841121495</v>
@@ -11632,7 +11649,7 @@
         <v>208</v>
       </c>
       <c r="B648" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D648" s="1">
         <v>698.36448598130801</v>
@@ -11646,7 +11663,7 @@
         <v>209</v>
       </c>
       <c r="B649" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D649" s="1">
         <v>522.63401720714705</v>
@@ -11660,7 +11677,7 @@
         <v>209</v>
       </c>
       <c r="B650" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D650" s="1">
         <v>572.66710787557895</v>
@@ -11674,7 +11691,7 @@
         <v>209</v>
       </c>
       <c r="B651" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D651" s="1">
         <v>622.70019854401005</v>
@@ -11688,7 +11705,7 @@
         <v>209</v>
       </c>
       <c r="B652" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D652" s="1">
         <v>672.73328921244195</v>
@@ -11702,7 +11719,7 @@
         <v>209</v>
       </c>
       <c r="B653" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D653" s="1">
         <v>773.19655857048303</v>
@@ -11716,7 +11733,7 @@
         <v>209</v>
       </c>
       <c r="B654" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D654" s="1">
         <v>872.86565188616805</v>
@@ -11730,7 +11747,7 @@
         <v>209</v>
       </c>
       <c r="B655" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D655" s="1">
         <v>972.93183322303105</v>
@@ -11744,7 +11761,7 @@
         <v>209</v>
       </c>
       <c r="B656" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D656" s="1">
         <v>1072.6009265387099</v>
@@ -11758,7 +11775,7 @@
         <v>210</v>
       </c>
       <c r="B657" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D657" s="34">
         <v>993.01377726750798</v>
@@ -11775,7 +11792,7 @@
         <v>210</v>
       </c>
       <c r="B658" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D658" s="34">
         <v>993.01377726750798</v>
@@ -11792,7 +11809,7 @@
         <v>210</v>
       </c>
       <c r="B659" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D659" s="34">
         <v>1013.00803673938</v>
@@ -11809,7 +11826,7 @@
         <v>210</v>
       </c>
       <c r="B660" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D660" s="34">
         <v>1013.00803673938</v>
@@ -11826,7 +11843,7 @@
         <v>210</v>
       </c>
       <c r="B661" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D661" s="34">
         <v>1033.00229621125</v>
@@ -11843,7 +11860,7 @@
         <v>210</v>
       </c>
       <c r="B662" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D662" s="1">
         <v>1033.00229621125</v>
@@ -11858,7 +11875,7 @@
         <v>210</v>
       </c>
       <c r="B663" s="30" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D663" s="1">
         <v>1052.9965556831201</v>
@@ -11873,7 +11890,7 @@
         <v>220</v>
       </c>
       <c r="B664" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D664" s="1">
         <v>722.73280584297004</v>
@@ -11887,7 +11904,7 @@
         <v>220</v>
       </c>
       <c r="B665" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D665" s="1">
         <v>772.94583079732195</v>
@@ -11901,7 +11918,7 @@
         <v>220</v>
       </c>
       <c r="B666" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D666" s="1">
         <v>822.85453438831405</v>
@@ -11915,7 +11932,7 @@
         <v>220</v>
       </c>
       <c r="B667" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D667" s="1">
         <v>873.06755934266505</v>
@@ -11929,7 +11946,7 @@
         <v>220</v>
       </c>
       <c r="B668" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D668" s="1">
         <v>922.97626293365704</v>
@@ -11943,7 +11960,7 @@
         <v>220</v>
       </c>
       <c r="B669" s="30" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="D669" s="1">
         <v>973.18928788800895</v>
@@ -11957,7 +11974,7 @@
         <v>230</v>
       </c>
       <c r="B670" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D670" s="1">
         <v>742</v>
@@ -11971,7 +11988,7 @@
         <v>230</v>
       </c>
       <c r="B671" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D671" s="1">
         <v>748</v>
@@ -11985,7 +12002,7 @@
         <v>240</v>
       </c>
       <c r="B672" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D672" s="1">
         <v>750.14153147936395</v>
@@ -11999,7 +12016,7 @@
         <v>240</v>
       </c>
       <c r="B673" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D673" s="1">
         <v>752.13939601477898</v>
@@ -12013,7 +12030,7 @@
         <v>240</v>
       </c>
       <c r="B674" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D674" s="1">
         <v>766.52402066976799</v>
@@ -12027,7 +12044,7 @@
         <v>240</v>
       </c>
       <c r="B675" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D675" s="1">
         <v>763.19424644407604</v>
@@ -12041,7 +12058,7 @@
         <v>240</v>
       </c>
       <c r="B676" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D676" s="1">
         <v>748.14366694394801</v>
@@ -12055,7 +12072,7 @@
         <v>240</v>
       </c>
       <c r="B677" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D677" s="1">
         <v>746.27899337756105</v>
@@ -12069,7 +12086,7 @@
         <v>240</v>
       </c>
       <c r="B678" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D678" s="1">
         <v>757.20065283783094</v>
@@ -12083,7 +12100,7 @@
         <v>240</v>
       </c>
       <c r="B679" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D679" s="1">
         <v>759.33170834227303</v>
@@ -12097,7 +12114,7 @@
         <v>240</v>
       </c>
       <c r="B680" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D680" s="1">
         <v>761.72914578477196</v>
@@ -12111,7 +12128,7 @@
         <v>240</v>
       </c>
       <c r="B681" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D681" s="1">
         <v>771.31889555476505</v>
@@ -12125,7 +12142,7 @@
         <v>240</v>
       </c>
       <c r="B682" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D682" s="1">
         <v>766.39082970074105</v>
@@ -12139,7 +12156,7 @@
         <v>240</v>
       </c>
       <c r="B683" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D683" s="1">
         <v>774.91505171851202</v>
@@ -12153,7 +12170,7 @@
         <v>240</v>
       </c>
       <c r="B684" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D684" s="1">
         <v>781.44140920086795</v>
@@ -12167,7 +12184,7 @@
         <v>240</v>
       </c>
       <c r="B685" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D685" s="1">
         <v>784.10522858142201</v>
@@ -12181,7 +12198,7 @@
         <v>240</v>
       </c>
       <c r="B686" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D686" s="1">
         <v>796.89156160807897</v>
@@ -12195,7 +12212,7 @@
         <v>240</v>
       </c>
       <c r="B687" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D687" s="1">
         <v>797.95708936030098</v>
@@ -12209,7 +12226,7 @@
         <v>240</v>
       </c>
       <c r="B688" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D688" s="1">
         <v>795.69284288683002</v>
@@ -12223,7 +12240,7 @@
         <v>240</v>
       </c>
       <c r="B689" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D689" s="1">
         <v>793.56178738238702</v>
@@ -12237,7 +12254,7 @@
         <v>240</v>
       </c>
       <c r="B690" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D690" s="1">
         <v>789.03329443544601</v>
@@ -12251,7 +12268,7 @@
         <v>240</v>
       </c>
       <c r="B691" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D691" s="1">
         <v>804.08387393557405</v>
@@ -12265,7 +12282,7 @@
         <v>240</v>
       </c>
       <c r="B692" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D692" s="1">
         <v>816.33744308612097</v>
@@ -12279,7 +12296,7 @@
         <v>240</v>
       </c>
       <c r="B693" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D693" s="1">
         <v>823.39656444458797</v>
@@ -12293,7 +12310,7 @@
         <v>240</v>
       </c>
       <c r="B694" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D694" s="1">
         <v>824.86166510389205</v>
@@ -12307,7 +12324,7 @@
         <v>240</v>
       </c>
       <c r="B695" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D695" s="1">
         <v>829.12377611277805</v>
@@ -12321,7 +12338,7 @@
         <v>240</v>
       </c>
       <c r="B696" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D696" s="1">
         <v>835.51694262610704</v>
@@ -12335,7 +12352,7 @@
         <v>240</v>
       </c>
       <c r="B697" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D697" s="1">
         <v>826.32676576319705</v>
@@ -12349,7 +12366,7 @@
         <v>240</v>
       </c>
       <c r="B698" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D698" s="1">
         <v>822.99699153750498</v>
@@ -12363,7 +12380,7 @@
         <v>240</v>
       </c>
       <c r="B699" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D699" s="1">
         <v>820.99912700208995</v>
@@ -12377,7 +12394,7 @@
         <v>240</v>
       </c>
       <c r="B700" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D700" s="1">
         <v>818.335307621536</v>
@@ -12391,7 +12408,7 @@
         <v>240</v>
       </c>
       <c r="B701" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D701" s="1">
         <v>855.76196991831398</v>
@@ -12405,7 +12422,7 @@
         <v>240</v>
       </c>
       <c r="B702" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D702" s="1">
         <v>852.83176859970501</v>
@@ -12419,7 +12436,7 @@
         <v>240</v>
       </c>
       <c r="B703" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D703" s="1">
         <v>866.81682034761104</v>
@@ -12433,7 +12450,7 @@
         <v>240</v>
       </c>
       <c r="B704" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D704" s="1">
         <v>878.271243683992</v>
@@ -12447,7 +12464,7 @@
         <v>240</v>
       </c>
       <c r="B705" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D705" s="1">
         <v>873.60955976802302</v>
@@ -12461,7 +12478,7 @@
         <v>240</v>
       </c>
       <c r="B706" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D706" s="1">
         <v>878.271243683992</v>
@@ -12475,7 +12492,7 @@
         <v>240</v>
       </c>
       <c r="B707" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D707" s="1">
         <v>875.07466042732801</v>
@@ -12489,7 +12506,7 @@
         <v>240</v>
       </c>
       <c r="B708" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D708" s="1">
         <v>870.67935844941405</v>
@@ -12503,7 +12520,7 @@
         <v>240</v>
       </c>
       <c r="B709" s="30" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="D709" s="1">
         <v>874.94146945830005</v>
@@ -12517,7 +12534,7 @@
         <v>250</v>
       </c>
       <c r="B710" s="33" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C710" s="31"/>
       <c r="D710" s="1">
@@ -12532,7 +12549,7 @@
         <v>250</v>
       </c>
       <c r="B711" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C711" s="3"/>
       <c r="D711" s="1">
@@ -12547,7 +12564,7 @@
         <v>250</v>
       </c>
       <c r="B712" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C712" s="3"/>
       <c r="D712" s="1">
@@ -12562,7 +12579,7 @@
         <v>250</v>
       </c>
       <c r="B713" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C713" s="3"/>
       <c r="D713" s="1">
@@ -12577,7 +12594,7 @@
         <v>250</v>
       </c>
       <c r="B714" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C714" s="3"/>
       <c r="D714" s="1">
@@ -12592,7 +12609,7 @@
         <v>250</v>
       </c>
       <c r="B715" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C715" s="3"/>
       <c r="D715" s="1">
@@ -12607,7 +12624,7 @@
         <v>250</v>
       </c>
       <c r="B716" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C716" s="3"/>
       <c r="D716" s="1">
@@ -12622,7 +12639,7 @@
         <v>260</v>
       </c>
       <c r="B717" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D717" s="1">
         <v>733</v>
@@ -12637,7 +12654,7 @@
         <v>260</v>
       </c>
       <c r="B718" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D718" s="1">
         <v>755</v>
@@ -12652,7 +12669,7 @@
         <v>260</v>
       </c>
       <c r="B719" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D719" s="1">
         <v>777</v>
@@ -12667,7 +12684,7 @@
         <v>260</v>
       </c>
       <c r="B720" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D720" s="1">
         <v>799</v>
@@ -12682,7 +12699,7 @@
         <v>260</v>
       </c>
       <c r="B721" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D721" s="1">
         <v>821</v>
@@ -12697,7 +12714,7 @@
         <v>260</v>
       </c>
       <c r="B722" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D722" s="1">
         <v>843</v>
@@ -12712,7 +12729,7 @@
         <v>260</v>
       </c>
       <c r="B723" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D723" s="1">
         <v>865</v>
@@ -12727,7 +12744,7 @@
         <v>260</v>
       </c>
       <c r="B724" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D724" s="1">
         <v>887</v>
@@ -12742,7 +12759,7 @@
         <v>260</v>
       </c>
       <c r="B725" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D725" s="1">
         <v>909</v>
@@ -12757,7 +12774,7 @@
         <v>260</v>
       </c>
       <c r="B726" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D726" s="1">
         <v>931</v>
@@ -12772,7 +12789,7 @@
         <v>260</v>
       </c>
       <c r="B727" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D727" s="1">
         <v>953</v>
@@ -12787,7 +12804,7 @@
         <v>260</v>
       </c>
       <c r="B728" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D728" s="1">
         <v>975</v>
@@ -12802,7 +12819,7 @@
         <v>260</v>
       </c>
       <c r="B729" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D729" s="1">
         <v>997</v>
@@ -12817,7 +12834,7 @@
         <v>260</v>
       </c>
       <c r="B730" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D730" s="1">
         <v>1019</v>
@@ -12832,7 +12849,7 @@
         <v>260</v>
       </c>
       <c r="B731" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D731" s="1">
         <v>1041</v>
@@ -12847,7 +12864,7 @@
         <v>260</v>
       </c>
       <c r="B732" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D732" s="1">
         <v>1063</v>
@@ -12862,7 +12879,7 @@
         <v>260</v>
       </c>
       <c r="B733" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D733" s="1">
         <v>1085</v>
@@ -12877,7 +12894,7 @@
         <v>260</v>
       </c>
       <c r="B734" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D734" s="1">
         <v>1107</v>
@@ -12892,7 +12909,7 @@
         <v>260</v>
       </c>
       <c r="B735" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D735" s="1">
         <v>1129</v>
@@ -12907,7 +12924,7 @@
         <v>260</v>
       </c>
       <c r="B736" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="D736" s="1">
         <v>1150</v>
@@ -12922,7 +12939,7 @@
         <v>270</v>
       </c>
       <c r="B737" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D737" s="1">
         <v>792.88235294117601</v>
@@ -12936,7 +12953,7 @@
         <v>270</v>
       </c>
       <c r="B738" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D738" s="1">
         <v>872.82352941176396</v>
@@ -12950,7 +12967,7 @@
         <v>270</v>
       </c>
       <c r="B739" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D739" s="1">
         <v>922.94117647058795</v>
@@ -12964,7 +12981,7 @@
         <v>270</v>
       </c>
       <c r="B740" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D740" s="1">
         <v>972.88235294117601</v>
@@ -12978,7 +12995,7 @@
         <v>280</v>
       </c>
       <c r="B741" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D741" s="1">
         <v>822.88235294117601</v>
@@ -12992,7 +13009,7 @@
         <v>280</v>
       </c>
       <c r="B742" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D742" s="1">
         <v>873</v>
@@ -13006,7 +13023,7 @@
         <v>280</v>
       </c>
       <c r="B743" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D743" s="1">
         <v>922.94117647058795</v>
@@ -13020,7 +13037,7 @@
         <v>280</v>
       </c>
       <c r="B744" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D744" s="1">
         <v>973.05882352941103</v>
@@ -13034,7 +13051,7 @@
         <v>290</v>
       </c>
       <c r="B745" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D745" s="1">
         <v>792.94975688816805</v>
@@ -13048,7 +13065,7 @@
         <v>290</v>
       </c>
       <c r="B746" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D746" s="1">
         <v>822.93354943273903</v>
@@ -13062,7 +13079,7 @@
         <v>290</v>
       </c>
       <c r="B747" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D747" s="1">
         <v>923.01458670988598</v>
@@ -13076,7 +13093,7 @@
         <v>290</v>
       </c>
       <c r="B748" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D748" s="1">
         <v>1022.69043760129</v>
@@ -13090,7 +13107,7 @@
         <v>290</v>
       </c>
       <c r="B749" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D749" s="1">
         <v>1122.7714748784399</v>
@@ -13104,7 +13121,7 @@
         <v>290</v>
       </c>
       <c r="B750" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="D750" s="1">
         <v>1222.8525121555899</v>
@@ -13118,7 +13135,7 @@
         <v>300</v>
       </c>
       <c r="B751" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D751" s="1">
         <v>849.27066450567202</v>
@@ -13138,7 +13155,7 @@
         <v>300</v>
       </c>
       <c r="B752" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D752" s="1">
         <v>874.39222042139295</v>
@@ -13158,7 +13175,7 @@
         <v>300</v>
       </c>
       <c r="B753" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D753" s="1">
         <v>899.10858995137698</v>
@@ -13178,13 +13195,13 @@
         <v>310</v>
       </c>
       <c r="B754" t="s">
-        <v>156</v>
-      </c>
-      <c r="D754" s="1">
-        <v>1100</v>
+        <v>175</v>
+      </c>
+      <c r="D754">
+        <v>1070</v>
       </c>
       <c r="E754" s="1">
-        <v>1.4643086816720201</v>
+        <v>1.1213120000000001</v>
       </c>
     </row>
     <row r="755" spans="1:9" x14ac:dyDescent="0.25">
@@ -13192,13 +13209,13 @@
         <v>310</v>
       </c>
       <c r="B755" t="s">
-        <v>156</v>
-      </c>
-      <c r="D755" s="1">
-        <v>1199.88998899889</v>
+        <v>175</v>
+      </c>
+      <c r="D755">
+        <v>1080</v>
       </c>
       <c r="E755" s="1">
-        <v>1.14769560557341</v>
+        <v>1.2564552000000002</v>
       </c>
     </row>
     <row r="756" spans="1:9" x14ac:dyDescent="0.25">
@@ -13206,128 +13223,125 @@
         <v>310</v>
       </c>
       <c r="B756" t="s">
-        <v>156</v>
-      </c>
-      <c r="D756" s="1">
-        <v>1249.8349834983401</v>
+        <v>175</v>
+      </c>
+      <c r="D756">
+        <v>1090</v>
       </c>
       <c r="E756" s="1">
-        <v>1.32775991425509</v>
+        <v>1.3698416000000002</v>
       </c>
     </row>
     <row r="757" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A757" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B757" t="s">
-        <v>157</v>
-      </c>
-      <c r="D757" s="1">
-        <v>1099.77997799779</v>
+        <v>175</v>
+      </c>
+      <c r="D757">
+        <v>1100</v>
       </c>
       <c r="E757" s="1">
-        <v>1.0171489817792001</v>
+        <v>1.4623080000000002</v>
       </c>
     </row>
     <row r="758" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A758" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B758" t="s">
-        <v>157</v>
-      </c>
-      <c r="D758" s="1">
-        <v>1199.88998899889</v>
+        <v>175</v>
+      </c>
+      <c r="D758">
+        <v>1110</v>
       </c>
       <c r="E758" s="1">
-        <v>0.99914255091103898</v>
+        <v>1.5330176</v>
       </c>
     </row>
     <row r="759" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A759" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B759" t="s">
-        <v>157</v>
-      </c>
-      <c r="D759" s="1">
-        <v>1249.8349834983401</v>
+        <v>175</v>
+      </c>
+      <c r="D759">
+        <v>1120</v>
       </c>
       <c r="E759" s="1">
-        <v>0.98713826366559398</v>
+        <v>1.5823888000000002</v>
       </c>
     </row>
     <row r="760" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A760" s="2">
-        <v>320</v>
+        <v>310</v>
       </c>
       <c r="B760" t="s">
-        <v>157</v>
-      </c>
-      <c r="D760" s="1">
-        <v>1300</v>
+        <v>175</v>
+      </c>
+      <c r="D760">
+        <v>1130</v>
       </c>
       <c r="E760" s="1">
-        <v>0.98413719185423298</v>
+        <v>1.6095848000000004</v>
       </c>
     </row>
     <row r="761" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A761" s="2">
-        <v>330</v>
-      </c>
-      <c r="B761" s="38" t="s">
-        <v>158</v>
+        <v>320</v>
+      </c>
+      <c r="B761" t="s">
+        <v>155</v>
       </c>
       <c r="D761" s="1">
-        <v>600</v>
+        <v>1099.77997799779</v>
       </c>
       <c r="E761" s="1">
-        <v>0.69</v>
-      </c>
-      <c r="I761" t="s">
-        <v>159</v>
+        <v>1.0171489817792001</v>
       </c>
     </row>
     <row r="762" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A762" s="2">
-        <v>330</v>
-      </c>
-      <c r="B762" s="38" t="s">
-        <v>158</v>
+        <v>320</v>
+      </c>
+      <c r="B762" t="s">
+        <v>155</v>
       </c>
       <c r="D762" s="1">
-        <v>620</v>
+        <v>1199.88998899889</v>
       </c>
       <c r="E762" s="1">
-        <v>0.69</v>
+        <v>0.99914255091103898</v>
       </c>
     </row>
     <row r="763" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A763" s="2">
-        <v>330</v>
-      </c>
-      <c r="B763" s="38" t="s">
-        <v>158</v>
+        <v>320</v>
+      </c>
+      <c r="B763" t="s">
+        <v>155</v>
       </c>
       <c r="D763" s="1">
-        <v>640</v>
+        <v>1249.8349834983401</v>
       </c>
       <c r="E763" s="1">
-        <v>0.69</v>
+        <v>0.98713826366559398</v>
       </c>
     </row>
     <row r="764" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A764" s="2">
-        <v>330</v>
-      </c>
-      <c r="B764" s="38" t="s">
-        <v>158</v>
+        <v>320</v>
+      </c>
+      <c r="B764" t="s">
+        <v>155</v>
       </c>
       <c r="D764" s="1">
-        <v>660</v>
+        <v>1300</v>
       </c>
       <c r="E764" s="1">
-        <v>0.69</v>
+        <v>0.98413719185423298</v>
       </c>
     </row>
     <row r="765" spans="1:9" x14ac:dyDescent="0.25">
@@ -13335,13 +13349,16 @@
         <v>330</v>
       </c>
       <c r="B765" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D765" s="1">
-        <v>680</v>
+        <v>600</v>
       </c>
       <c r="E765" s="1">
         <v>0.69</v>
+      </c>
+      <c r="I765" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="766" spans="1:9" x14ac:dyDescent="0.25">
@@ -13349,10 +13366,10 @@
         <v>330</v>
       </c>
       <c r="B766" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D766" s="1">
-        <v>700</v>
+        <v>620</v>
       </c>
       <c r="E766" s="1">
         <v>0.69</v>
@@ -13363,10 +13380,10 @@
         <v>330</v>
       </c>
       <c r="B767" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D767" s="1">
-        <v>720</v>
+        <v>640</v>
       </c>
       <c r="E767" s="1">
         <v>0.69</v>
@@ -13377,10 +13394,10 @@
         <v>330</v>
       </c>
       <c r="B768" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D768" s="1">
-        <v>740</v>
+        <v>660</v>
       </c>
       <c r="E768" s="1">
         <v>0.69</v>
@@ -13391,10 +13408,10 @@
         <v>330</v>
       </c>
       <c r="B769" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D769" s="1">
-        <v>760</v>
+        <v>680</v>
       </c>
       <c r="E769" s="1">
         <v>0.69</v>
@@ -13405,10 +13422,10 @@
         <v>330</v>
       </c>
       <c r="B770" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D770" s="1">
-        <v>780</v>
+        <v>700</v>
       </c>
       <c r="E770" s="1">
         <v>0.69</v>
@@ -13419,10 +13436,10 @@
         <v>330</v>
       </c>
       <c r="B771" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D771" s="1">
-        <v>800</v>
+        <v>720</v>
       </c>
       <c r="E771" s="1">
         <v>0.69</v>
@@ -13433,10 +13450,10 @@
         <v>330</v>
       </c>
       <c r="B772" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D772" s="1">
-        <v>820</v>
+        <v>740</v>
       </c>
       <c r="E772" s="1">
         <v>0.69</v>
@@ -13447,10 +13464,10 @@
         <v>330</v>
       </c>
       <c r="B773" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D773" s="1">
-        <v>840</v>
+        <v>760</v>
       </c>
       <c r="E773" s="1">
         <v>0.69</v>
@@ -13461,10 +13478,10 @@
         <v>330</v>
       </c>
       <c r="B774" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D774" s="1">
-        <v>860</v>
+        <v>780</v>
       </c>
       <c r="E774" s="1">
         <v>0.69</v>
@@ -13475,10 +13492,10 @@
         <v>330</v>
       </c>
       <c r="B775" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D775" s="1">
-        <v>880</v>
+        <v>800</v>
       </c>
       <c r="E775" s="1">
         <v>0.69</v>
@@ -13489,10 +13506,10 @@
         <v>330</v>
       </c>
       <c r="B776" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D776" s="1">
-        <v>900</v>
+        <v>820</v>
       </c>
       <c r="E776" s="1">
         <v>0.69</v>
@@ -13503,10 +13520,10 @@
         <v>330</v>
       </c>
       <c r="B777" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D777" s="1">
-        <v>920</v>
+        <v>840</v>
       </c>
       <c r="E777" s="1">
         <v>0.69</v>
@@ -13517,10 +13534,10 @@
         <v>330</v>
       </c>
       <c r="B778" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D778" s="1">
-        <v>940</v>
+        <v>860</v>
       </c>
       <c r="E778" s="1">
         <v>0.69</v>
@@ -13531,10 +13548,10 @@
         <v>330</v>
       </c>
       <c r="B779" s="38" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="D779" s="1">
-        <v>960</v>
+        <v>880</v>
       </c>
       <c r="E779" s="1">
         <v>0.69</v>
@@ -13542,310 +13559,310 @@
     </row>
     <row r="780" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A780" s="2">
-        <v>341</v>
-      </c>
-      <c r="B780" s="1" t="s">
-        <v>160</v>
+        <v>330</v>
+      </c>
+      <c r="B780" s="38" t="s">
+        <v>156</v>
       </c>
       <c r="D780" s="1">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="E780" s="1">
-        <v>0.459822090437361</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="781" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A781" s="2">
-        <v>341</v>
-      </c>
-      <c r="B781" s="1" t="s">
-        <v>160</v>
+        <v>330</v>
+      </c>
+      <c r="B781" s="38" t="s">
+        <v>156</v>
       </c>
       <c r="D781" s="1">
-        <v>1200</v>
+        <v>920</v>
       </c>
       <c r="E781" s="1">
-        <v>0.459822090437361</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="782" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A782" s="2">
-        <v>342</v>
-      </c>
-      <c r="B782" s="1" t="s">
-        <v>161</v>
+        <v>330</v>
+      </c>
+      <c r="B782" s="38" t="s">
+        <v>156</v>
       </c>
       <c r="D782" s="1">
-        <v>1000</v>
+        <v>940</v>
       </c>
       <c r="E782" s="1">
-        <v>0.460711638250556</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="783" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A783" s="2">
-        <v>342</v>
-      </c>
-      <c r="B783" s="1" t="s">
-        <v>161</v>
+        <v>330</v>
+      </c>
+      <c r="B783" s="38" t="s">
+        <v>156</v>
       </c>
       <c r="D783" s="1">
-        <v>1200</v>
+        <v>960</v>
       </c>
       <c r="E783" s="1">
-        <v>0.460711638250556</v>
+        <v>0.69</v>
       </c>
     </row>
     <row r="784" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A784" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B784" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D784" s="1">
         <v>1000</v>
       </c>
       <c r="E784" s="1">
-        <v>0.49162342475908</v>
+        <v>0.459822090437361</v>
       </c>
     </row>
     <row r="785" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A785" s="2">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B785" s="1" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="D785" s="1">
         <v>1200</v>
       </c>
       <c r="E785" s="1">
-        <v>0.49162342475908</v>
+        <v>0.459822090437361</v>
       </c>
     </row>
     <row r="786" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A786" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B786" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D786" s="1">
         <v>1000</v>
       </c>
       <c r="E786" s="1">
-        <v>0.494292068198665</v>
+        <v>0.460711638250556</v>
       </c>
     </row>
     <row r="787" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A787" s="2">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="B787" s="1" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="D787" s="1">
         <v>1200</v>
       </c>
       <c r="E787" s="1">
-        <v>0.494292068198665</v>
+        <v>0.460711638250556</v>
       </c>
     </row>
     <row r="788" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A788" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B788" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D788" s="1">
         <v>1000</v>
       </c>
       <c r="E788" s="1">
-        <v>0.51786508524833197</v>
+        <v>0.49162342475908</v>
       </c>
     </row>
     <row r="789" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A789" s="2">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="B789" s="1" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="D789" s="1">
         <v>1200</v>
       </c>
       <c r="E789" s="1">
-        <v>0.51786508524833197</v>
+        <v>0.49162342475908</v>
       </c>
     </row>
     <row r="790" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A790" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B790" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D790" s="1">
         <v>1000</v>
       </c>
       <c r="E790" s="1">
-        <v>0.55255744996293499</v>
+        <v>0.494292068198665</v>
       </c>
     </row>
     <row r="791" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A791" s="2">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B791" s="1" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="D791" s="1">
         <v>1200</v>
       </c>
       <c r="E791" s="1">
-        <v>0.55255744996293499</v>
+        <v>0.494292068198665</v>
       </c>
     </row>
     <row r="792" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A792" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B792" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D792" s="1">
         <v>1000</v>
       </c>
       <c r="E792" s="1">
-        <v>0.58413639733135603</v>
+        <v>0.51786508524833197</v>
       </c>
     </row>
     <row r="793" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A793" s="2">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B793" s="1" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="D793" s="1">
         <v>1200</v>
       </c>
       <c r="E793" s="1">
-        <v>0.58413639733135603</v>
+        <v>0.51786508524833197</v>
       </c>
     </row>
     <row r="794" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A794" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B794" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D794" s="1">
         <v>1000</v>
       </c>
       <c r="E794" s="1">
-        <v>0.60748702742772398</v>
+        <v>0.55255744996293499</v>
       </c>
     </row>
     <row r="795" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A795" s="2">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B795" s="1" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D795" s="1">
         <v>1200</v>
       </c>
       <c r="E795" s="1">
-        <v>0.60748702742772398</v>
+        <v>0.55255744996293499</v>
       </c>
     </row>
     <row r="796" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A796" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B796" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D796" s="1">
         <v>1000</v>
       </c>
       <c r="E796" s="1">
-        <v>0.673091178650852</v>
+        <v>0.58413639733135603</v>
       </c>
     </row>
     <row r="797" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A797" s="2">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B797" s="1" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="D797" s="1">
         <v>1200</v>
       </c>
       <c r="E797" s="1">
-        <v>0.673091178650852</v>
+        <v>0.58413639733135603</v>
       </c>
     </row>
     <row r="798" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A798" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B798" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D798" s="1">
-        <v>761.04532462229395</v>
+        <v>1000</v>
       </c>
       <c r="E798" s="1">
-        <v>0.59875486381322895</v>
+        <v>0.60748702742772398</v>
       </c>
     </row>
     <row r="799" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A799" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B799" s="1" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D799" s="1">
-        <v>811.02490812576502</v>
+        <v>1200</v>
       </c>
       <c r="E799" s="1">
-        <v>0.57073929961089498</v>
+        <v>0.60748702742772398</v>
       </c>
     </row>
     <row r="800" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A800" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B800" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D800" s="1">
-        <v>860.02449979583503</v>
+        <v>1000</v>
       </c>
       <c r="E800" s="1">
-        <v>0.51657587548638095</v>
+        <v>0.673091178650852</v>
       </c>
     </row>
     <row r="801" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A801" s="2">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="B801" s="1" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="D801" s="1">
-        <v>908.37076357697003</v>
+        <v>1200</v>
       </c>
       <c r="E801" s="1">
-        <v>0.498365758754864</v>
+        <v>0.673091178650852</v>
       </c>
     </row>
     <row r="802" spans="1:5" x14ac:dyDescent="0.25">
@@ -13853,13 +13870,13 @@
         <v>350</v>
       </c>
       <c r="B802" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D802" s="1">
-        <v>958.350347080441</v>
+        <v>761.04532462229395</v>
       </c>
       <c r="E802" s="1">
-        <v>0.49042801556420201</v>
+        <v>0.59875486381322895</v>
       </c>
     </row>
     <row r="803" spans="1:5" x14ac:dyDescent="0.25">
@@ -13867,69 +13884,69 @@
         <v>350</v>
       </c>
       <c r="B803" s="1" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D803" s="1">
-        <v>1008.32993058391</v>
+        <v>811.02490812576502</v>
       </c>
       <c r="E803" s="1">
-        <v>0.50256809338521402</v>
+        <v>0.57073929961089498</v>
       </c>
     </row>
     <row r="804" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A804" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B804" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D804">
-        <v>949.26108374384205</v>
-      </c>
-      <c r="E804">
-        <v>0.48016284233900802</v>
+        <v>167</v>
+      </c>
+      <c r="D804" s="1">
+        <v>860.02449979583503</v>
+      </c>
+      <c r="E804" s="1">
+        <v>0.51657587548638095</v>
       </c>
     </row>
     <row r="805" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A805" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B805" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D805">
-        <v>948.97959183673402</v>
-      </c>
-      <c r="E805">
-        <v>0.35181347150259001</v>
+        <v>167</v>
+      </c>
+      <c r="D805" s="1">
+        <v>908.37076357697003</v>
+      </c>
+      <c r="E805" s="1">
+        <v>0.498365758754864</v>
       </c>
     </row>
     <row r="806" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A806" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B806" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D806">
-        <v>949.54257565094997</v>
-      </c>
-      <c r="E806">
-        <v>0.32561065877127998</v>
+        <v>167</v>
+      </c>
+      <c r="D806" s="1">
+        <v>958.350347080441</v>
+      </c>
+      <c r="E806" s="1">
+        <v>0.49042801556420201</v>
       </c>
     </row>
     <row r="807" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A807" s="2">
-        <v>360</v>
+        <v>350</v>
       </c>
       <c r="B807" s="1" t="s">
-        <v>170</v>
-      </c>
-      <c r="D807">
-        <v>948.69809992962701</v>
-      </c>
-      <c r="E807">
-        <v>0.31806069578090201</v>
+        <v>167</v>
+      </c>
+      <c r="D807" s="1">
+        <v>1008.32993058391</v>
+      </c>
+      <c r="E807" s="1">
+        <v>0.50256809338521402</v>
       </c>
     </row>
     <row r="808" spans="1:5" x14ac:dyDescent="0.25">
@@ -13937,13 +13954,13 @@
         <v>360</v>
       </c>
       <c r="B808" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D808">
-        <v>948.97959183673402</v>
+        <v>949.26108374384205</v>
       </c>
       <c r="E808">
-        <v>0.280754996299037</v>
+        <v>0.48016284233900802</v>
       </c>
     </row>
     <row r="809" spans="1:5" x14ac:dyDescent="0.25">
@@ -13951,13 +13968,13 @@
         <v>360</v>
       </c>
       <c r="B809" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D809">
-        <v>974.31386347642501</v>
+        <v>948.97959183673402</v>
       </c>
       <c r="E809">
-        <v>0.280754996299037</v>
+        <v>0.35181347150259001</v>
       </c>
     </row>
     <row r="810" spans="1:5" x14ac:dyDescent="0.25">
@@ -13965,13 +13982,13 @@
         <v>360</v>
       </c>
       <c r="B810" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D810">
-        <v>974.31386347642501</v>
+        <v>949.54257565094997</v>
       </c>
       <c r="E810">
-        <v>0.35492227979274599</v>
+        <v>0.32561065877127998</v>
       </c>
     </row>
     <row r="811" spans="1:5" x14ac:dyDescent="0.25">
@@ -13979,13 +13996,13 @@
         <v>360</v>
       </c>
       <c r="B811" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D811">
-        <v>974.31386347642501</v>
+        <v>948.69809992962701</v>
       </c>
       <c r="E811">
-        <v>0.36247224278312301</v>
+        <v>0.31806069578090201</v>
       </c>
     </row>
     <row r="812" spans="1:5" x14ac:dyDescent="0.25">
@@ -13993,13 +14010,13 @@
         <v>360</v>
       </c>
       <c r="B812" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D812">
-        <v>1003.30752990851</v>
+        <v>948.97959183673402</v>
       </c>
       <c r="E812">
-        <v>0.360695780903034</v>
+        <v>0.280754996299037</v>
       </c>
     </row>
     <row r="813" spans="1:5" x14ac:dyDescent="0.25">
@@ -14007,13 +14024,13 @@
         <v>360</v>
       </c>
       <c r="B813" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D813">
-        <v>1004.99648135116</v>
+        <v>974.31386347642501</v>
       </c>
       <c r="E813">
-        <v>0.31761658031088003</v>
+        <v>0.280754996299037</v>
       </c>
     </row>
     <row r="814" spans="1:5" x14ac:dyDescent="0.25">
@@ -14021,13 +14038,13 @@
         <v>360</v>
       </c>
       <c r="B814" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D814">
-        <v>1004.15200562983</v>
+        <v>974.31386347642501</v>
       </c>
       <c r="E814">
-        <v>0.30518134715025902</v>
+        <v>0.35492227979274599</v>
       </c>
     </row>
     <row r="815" spans="1:5" x14ac:dyDescent="0.25">
@@ -14035,13 +14052,13 @@
         <v>360</v>
       </c>
       <c r="B815" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D815">
-        <v>1003.30752990851</v>
+        <v>974.31386347642501</v>
       </c>
       <c r="E815">
-        <v>0.29008142116950397</v>
+        <v>0.36247224278312301</v>
       </c>
     </row>
     <row r="816" spans="1:5" x14ac:dyDescent="0.25">
@@ -14049,13 +14066,13 @@
         <v>360</v>
       </c>
       <c r="B816" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D816">
-        <v>1044.4053483462301</v>
+        <v>1003.30752990851</v>
       </c>
       <c r="E816">
-        <v>0.28430792005921501</v>
+        <v>0.360695780903034</v>
       </c>
     </row>
     <row r="817" spans="1:5" x14ac:dyDescent="0.25">
@@ -14063,13 +14080,13 @@
         <v>360</v>
       </c>
       <c r="B817" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D817">
-        <v>1044.4053483462301</v>
+        <v>1004.99648135116</v>
       </c>
       <c r="E817">
-        <v>0.26343449296817101</v>
+        <v>0.31761658031088003</v>
       </c>
     </row>
     <row r="818" spans="1:5" x14ac:dyDescent="0.25">
@@ -14077,13 +14094,13 @@
         <v>360</v>
       </c>
       <c r="B818" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D818">
-        <v>1043.56087262491</v>
+        <v>1004.15200562983</v>
       </c>
       <c r="E818">
-        <v>0.25810510732790498</v>
+        <v>0.30518134715025902</v>
       </c>
     </row>
     <row r="819" spans="1:5" x14ac:dyDescent="0.25">
@@ -14091,13 +14108,13 @@
         <v>360</v>
       </c>
       <c r="B819" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D819">
-        <v>1082.68824771287</v>
+        <v>1003.30752990851</v>
       </c>
       <c r="E819">
-        <v>0.26920799407846002</v>
+        <v>0.29008142116950397</v>
       </c>
     </row>
     <row r="820" spans="1:5" x14ac:dyDescent="0.25">
@@ -14105,13 +14122,13 @@
         <v>360</v>
       </c>
       <c r="B820" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D820">
-        <v>1084.09570724841</v>
+        <v>1044.4053483462301</v>
       </c>
       <c r="E820">
-        <v>0.23678756476683899</v>
+        <v>0.28430792005921501</v>
       </c>
     </row>
     <row r="821" spans="1:5" x14ac:dyDescent="0.25">
@@ -14119,10 +14136,10 @@
         <v>360</v>
       </c>
       <c r="B821" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D821">
-        <v>1113.65235749472</v>
+        <v>1044.4053483462301</v>
       </c>
       <c r="E821">
         <v>0.26343449296817101</v>
@@ -14133,13 +14150,13 @@
         <v>360</v>
       </c>
       <c r="B822" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D822">
-        <v>1143.77199155524</v>
+        <v>1043.56087262491</v>
       </c>
       <c r="E822">
-        <v>0.280754996299037</v>
+        <v>0.25810510732790498</v>
       </c>
     </row>
     <row r="823" spans="1:5" x14ac:dyDescent="0.25">
@@ -14147,13 +14164,13 @@
         <v>360</v>
       </c>
       <c r="B823" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D823">
-        <v>1143.77199155524</v>
+        <v>1082.68824771287</v>
       </c>
       <c r="E823">
-        <v>0.21014063656550599</v>
+        <v>0.26920799407846002</v>
       </c>
     </row>
     <row r="824" spans="1:5" x14ac:dyDescent="0.25">
@@ -14161,13 +14178,13 @@
         <v>360</v>
       </c>
       <c r="B824" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D824">
-        <v>1143.49049964813</v>
+        <v>1084.09570724841</v>
       </c>
       <c r="E824">
-        <v>0.196373056994818</v>
+        <v>0.23678756476683899</v>
       </c>
     </row>
     <row r="825" spans="1:5" x14ac:dyDescent="0.25">
@@ -14175,69 +14192,69 @@
         <v>360</v>
       </c>
       <c r="B825" s="1" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="D825">
-        <v>953.76495425756502</v>
+        <v>1113.65235749472</v>
       </c>
       <c r="E825">
-        <v>0.457957068837897</v>
+        <v>0.26343449296817101</v>
       </c>
     </row>
     <row r="826" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A826" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B826" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D826">
-        <v>954.04644616467203</v>
+        <v>1143.77199155524</v>
       </c>
       <c r="E826">
-        <v>0.59385640266469197</v>
+        <v>0.280754996299037</v>
       </c>
     </row>
     <row r="827" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A827" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B827" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D827">
-        <v>952.92047853624194</v>
+        <v>1143.77199155524</v>
       </c>
       <c r="E827">
-        <v>0.45840118430791998</v>
+        <v>0.21014063656550599</v>
       </c>
     </row>
     <row r="828" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A828" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B828" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D828">
-        <v>988.66995073891599</v>
+        <v>1143.49049964813</v>
       </c>
       <c r="E828">
-        <v>0.45840118430791998</v>
+        <v>0.196373056994818</v>
       </c>
     </row>
     <row r="829" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A829" s="2">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="B829" s="1" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D829">
-        <v>988.66995073891599</v>
+        <v>953.76495425756502</v>
       </c>
       <c r="E829">
-        <v>0.40377498149518798</v>
+        <v>0.457957068837897</v>
       </c>
     </row>
     <row r="830" spans="1:5" x14ac:dyDescent="0.25">
@@ -14245,13 +14262,13 @@
         <v>370</v>
       </c>
       <c r="B830" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D830">
-        <v>988.66995073891599</v>
+        <v>954.04644616467203</v>
       </c>
       <c r="E830">
-        <v>0.38467801628423298</v>
+        <v>0.59385640266469197</v>
       </c>
     </row>
     <row r="831" spans="1:5" x14ac:dyDescent="0.25">
@@ -14259,13 +14276,13 @@
         <v>370</v>
       </c>
       <c r="B831" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D831">
-        <v>1033.4271639690301</v>
+        <v>952.92047853624194</v>
       </c>
       <c r="E831">
-        <v>0.38245743893412198</v>
+        <v>0.45840118430791998</v>
       </c>
     </row>
     <row r="832" spans="1:5" x14ac:dyDescent="0.25">
@@ -14273,13 +14290,13 @@
         <v>370</v>
       </c>
       <c r="B832" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D832">
-        <v>1033.70865587614</v>
+        <v>988.66995073891599</v>
       </c>
       <c r="E832">
-        <v>0.42864544781643199</v>
+        <v>0.45840118430791998</v>
       </c>
     </row>
     <row r="833" spans="1:5" x14ac:dyDescent="0.25">
@@ -14287,13 +14304,13 @@
         <v>370</v>
       </c>
       <c r="B833" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D833">
-        <v>1073.9619985925401</v>
+        <v>988.66995073891599</v>
       </c>
       <c r="E833">
-        <v>0.43841598815692001</v>
+        <v>0.40377498149518798</v>
       </c>
     </row>
     <row r="834" spans="1:5" x14ac:dyDescent="0.25">
@@ -14301,13 +14318,13 @@
         <v>370</v>
       </c>
       <c r="B834" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D834">
-        <v>1074.2434904996401</v>
+        <v>988.66995073891599</v>
       </c>
       <c r="E834">
-        <v>0.405107327905255</v>
+        <v>0.38467801628423298</v>
       </c>
     </row>
     <row r="835" spans="1:5" x14ac:dyDescent="0.25">
@@ -14315,138 +14332,194 @@
         <v>370</v>
       </c>
       <c r="B835" s="1" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D835">
-        <v>1073.9619985925401</v>
+        <v>1033.4271639690301</v>
       </c>
       <c r="E835">
-        <v>0.39400444115470001</v>
+        <v>0.38245743893412198</v>
       </c>
     </row>
     <row r="836" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A836" s="2">
-        <v>380</v>
+        <v>370</v>
       </c>
       <c r="B836" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D836">
-        <v>933.49753694581204</v>
+        <v>1033.70865587614</v>
       </c>
       <c r="E836">
-        <v>0.51658031088082801</v>
+        <v>0.42864544781643199</v>
       </c>
     </row>
     <row r="837" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A837" s="2">
-        <v>381</v>
+        <v>370</v>
       </c>
       <c r="B837" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D837">
-        <v>950.66854327937995</v>
+        <v>1073.9619985925401</v>
       </c>
       <c r="E837">
-        <v>0.40022205773501102</v>
+        <v>0.43841598815692001</v>
       </c>
     </row>
     <row r="838" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A838" s="2">
-        <v>382</v>
+        <v>370</v>
       </c>
       <c r="B838" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D838">
-        <v>971.49894440534797</v>
+        <v>1074.2434904996401</v>
       </c>
       <c r="E838">
-        <v>0.52413027387120603</v>
+        <v>0.405107327905255</v>
       </c>
     </row>
     <row r="839" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A839" s="2">
-        <v>383</v>
+        <v>370</v>
       </c>
       <c r="B839" s="1" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="D839">
-        <v>988.951442646023</v>
+        <v>1073.9619985925401</v>
       </c>
       <c r="E839">
-        <v>0.42376017764618701</v>
+        <v>0.39400444115470001</v>
       </c>
     </row>
     <row r="840" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A840" s="2">
+        <v>380</v>
+      </c>
+      <c r="B840" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D840">
+        <v>933.49753694581204</v>
+      </c>
+      <c r="E840">
+        <v>0.51658031088082801</v>
+      </c>
+    </row>
+    <row r="841" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A841" s="2">
+        <v>381</v>
+      </c>
+      <c r="B841" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D841">
+        <v>950.66854327937995</v>
+      </c>
+      <c r="E841">
+        <v>0.40022205773501102</v>
+      </c>
+    </row>
+    <row r="842" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A842" s="2">
+        <v>382</v>
+      </c>
+      <c r="B842" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D842">
+        <v>971.49894440534797</v>
+      </c>
+      <c r="E842">
+        <v>0.52413027387120603</v>
+      </c>
+    </row>
+    <row r="843" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A843" s="2">
+        <v>383</v>
+      </c>
+      <c r="B843" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D843">
+        <v>988.951442646023</v>
+      </c>
+      <c r="E843">
+        <v>0.42376017764618701</v>
+      </c>
+    </row>
+    <row r="844" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A844" s="2">
         <v>384</v>
       </c>
-      <c r="B840" s="1" t="s">
-        <v>172</v>
-      </c>
-      <c r="D840">
+      <c r="B844" s="1" t="s">
+        <v>170</v>
+      </c>
+      <c r="D844">
         <v>1009.50035186488</v>
       </c>
-      <c r="E840">
+      <c r="E844">
         <v>0.489489267209474</v>
-      </c>
-    </row>
-    <row r="841" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D841">
-        <v>749.595744680851</v>
-      </c>
-      <c r="E841">
-        <v>0.51921458625525896</v>
-      </c>
-    </row>
-    <row r="842" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D842">
-        <v>774.063829787234</v>
-      </c>
-      <c r="E842">
-        <v>0.48828892005609997</v>
-      </c>
-    </row>
-    <row r="843" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D843">
-        <v>799.063829787234</v>
-      </c>
-      <c r="E843">
-        <v>0.46136044880785398</v>
-      </c>
-    </row>
-    <row r="844" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="D844">
-        <v>824.32978723404199</v>
-      </c>
-      <c r="E844">
-        <v>0.46619915848527299</v>
       </c>
     </row>
     <row r="845" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D845">
-        <v>848.531914893617</v>
+        <v>749.595744680851</v>
       </c>
       <c r="E845">
-        <v>0.45589060308555401</v>
+        <v>0.51921458625525896</v>
       </c>
     </row>
     <row r="846" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D846">
-        <v>874.063829787234</v>
+        <v>774.063829787234</v>
       </c>
       <c r="E846">
-        <v>0.440322580645161</v>
+        <v>0.48828892005609997</v>
       </c>
     </row>
     <row r="847" spans="1:5" x14ac:dyDescent="0.25">
       <c r="D847">
+        <v>799.063829787234</v>
+      </c>
+      <c r="E847">
+        <v>0.46136044880785398</v>
+      </c>
+    </row>
+    <row r="848" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="D848">
+        <v>824.32978723404199</v>
+      </c>
+      <c r="E848">
+        <v>0.46619915848527299</v>
+      </c>
+    </row>
+    <row r="849" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D849">
+        <v>848.531914893617</v>
+      </c>
+      <c r="E849">
+        <v>0.45589060308555401</v>
+      </c>
+    </row>
+    <row r="850" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D850">
+        <v>874.063829787234</v>
+      </c>
+      <c r="E850">
+        <v>0.440322580645161</v>
+      </c>
+    </row>
+    <row r="851" spans="4:5" x14ac:dyDescent="0.25">
+      <c r="D851">
         <v>899.063829787234</v>
       </c>
-      <c r="E847">
+      <c r="E851">
         <v>0.42769985974754499</v>
       </c>
     </row>
@@ -14466,7 +14539,7 @@
         <v>230</v>
       </c>
       <c r="B1" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D1" s="1">
         <v>459</v>
@@ -14480,7 +14553,7 @@
         <v>230</v>
       </c>
       <c r="B2" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D2" s="1">
         <v>472</v>
@@ -14494,7 +14567,7 @@
         <v>230</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D3" s="1">
         <v>474</v>
@@ -14508,7 +14581,7 @@
         <v>230</v>
       </c>
       <c r="B4" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D4" s="1">
         <v>500</v>
@@ -14522,7 +14595,7 @@
         <v>230</v>
       </c>
       <c r="B5" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D5" s="1">
         <v>516</v>
@@ -14536,7 +14609,7 @@
         <v>230</v>
       </c>
       <c r="B6" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D6" s="1">
         <v>544</v>
@@ -14550,7 +14623,7 @@
         <v>230</v>
       </c>
       <c r="B7" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D7" s="1">
         <v>570</v>
@@ -14564,7 +14637,7 @@
         <v>230</v>
       </c>
       <c r="B8" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D8" s="1">
         <v>600</v>
@@ -14578,7 +14651,7 @@
         <v>230</v>
       </c>
       <c r="B9" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D9" s="1">
         <v>622</v>
@@ -14592,7 +14665,7 @@
         <v>230</v>
       </c>
       <c r="B10" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D10" s="1">
         <v>648</v>
@@ -14606,7 +14679,7 @@
         <v>230</v>
       </c>
       <c r="B11" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D11" s="1">
         <v>671</v>
@@ -14620,7 +14693,7 @@
         <v>230</v>
       </c>
       <c r="B12" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D12" s="1">
         <v>671</v>
@@ -14634,7 +14707,7 @@
         <v>230</v>
       </c>
       <c r="B13" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D13" s="1">
         <v>697</v>
@@ -14648,7 +14721,7 @@
         <v>230</v>
       </c>
       <c r="B14" s="30" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="D14" s="1">
         <v>720</v>
@@ -14672,37 +14745,37 @@
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C1" t="s">
         <v>94</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>95</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>96</v>
       </c>
-      <c r="E1" t="s">
+      <c r="G1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" t="s">
+        <v>100</v>
+      </c>
+      <c r="J1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L1" t="s">
+        <v>94</v>
+      </c>
+      <c r="M1" t="s">
+        <v>98</v>
+      </c>
+      <c r="N1" t="s">
         <v>97</v>
-      </c>
-      <c r="G1" t="s">
-        <v>94</v>
-      </c>
-      <c r="H1" t="s">
-        <v>95</v>
-      </c>
-      <c r="I1" t="s">
-        <v>101</v>
-      </c>
-      <c r="J1" t="s">
-        <v>100</v>
-      </c>
-      <c r="L1" t="s">
-        <v>95</v>
-      </c>
-      <c r="M1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N1" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.25">
@@ -14911,10 +14984,10 @@
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.25">
       <c r="C10" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D10" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.25">
@@ -17501,30 +17574,30 @@
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="D1" t="s">
+        <v>118</v>
+      </c>
+      <c r="E1" t="s">
         <v>119</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>120</v>
       </c>
-      <c r="F1" t="s">
-        <v>121</v>
-      </c>
       <c r="G1" t="s">
+        <v>128</v>
+      </c>
+      <c r="H1" t="s">
         <v>129</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>130</v>
       </c>
-      <c r="I1" t="s">
-        <v>131</v>
-      </c>
       <c r="K1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D2">
         <v>0.342095327984898</v>
@@ -17533,7 +17606,7 @@
         <v>2.2857142857142998</v>
       </c>
       <c r="F2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G2">
         <f>$G$7</f>
@@ -17556,7 +17629,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="D3">
         <v>0.342095327984898</v>
@@ -17565,7 +17638,7 @@
         <v>8.7619047619048303</v>
       </c>
       <c r="F3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G3">
         <f t="shared" ref="G3:G6" si="0">$G$7</f>
@@ -17588,7 +17661,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B4" s="36">
         <v>5.8439999999999999E-2</v>
@@ -17600,7 +17673,7 @@
         <v>9.6507936507937302</v>
       </c>
       <c r="F4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G4">
         <f t="shared" si="0"/>
@@ -17623,7 +17696,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B5" s="37">
         <v>0.34438790000000002</v>
@@ -17635,7 +17708,7 @@
         <v>12.888888888888999</v>
       </c>
       <c r="F5" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G5">
         <f t="shared" si="0"/>
@@ -17664,7 +17737,7 @@
         <v>66.666666666666501</v>
       </c>
       <c r="F6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G6">
         <f t="shared" si="0"/>
@@ -17687,13 +17760,13 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B7" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C7" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D7">
         <v>0.34179104477611899</v>
@@ -17709,10 +17782,10 @@
         <v>6.0040106951871426</v>
       </c>
       <c r="H7" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I7" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J7">
         <f>1+SUM(J2:J6)</f>
@@ -17768,7 +17841,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D12">
         <v>0.37012741859367598</v>
@@ -17777,7 +17850,7 @@
         <v>1.3968253968254001</v>
       </c>
       <c r="F12" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G12">
         <f>$G$17</f>
@@ -17806,7 +17879,7 @@
         <v>5.5873015873016101</v>
       </c>
       <c r="F13" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13">
         <f t="shared" ref="G13:G16" si="3">$G$17</f>
@@ -17835,7 +17908,7 @@
         <v>6.2857142857143602</v>
       </c>
       <c r="F14" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14">
         <f t="shared" si="3"/>
@@ -17864,7 +17937,7 @@
         <v>9.3333333333334494</v>
       </c>
       <c r="F15" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G15">
         <f t="shared" si="3"/>
@@ -17893,7 +17966,7 @@
         <v>77.460317460317398</v>
       </c>
       <c r="F16" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G16">
         <f t="shared" si="3"/>
@@ -17916,13 +17989,13 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B17" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C17" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D17">
         <v>0.37</v>
@@ -17938,10 +18011,10 @@
         <v>5.9832887700534636</v>
       </c>
       <c r="H17" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="I17" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="J17">
         <f>1+SUM(J12:J16)</f>
